--- a/docs/oc-mensuales/suministro-de-combustibles/nov-2025.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/nov-2025.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2244.32</v>
+        <v>2225.31</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>6946.69</v>
+        <v>6887.86</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>36336.53</v>
+        <v>36028.78</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2992.42</v>
+        <v>2967.08</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>26718.04</v>
+        <v>26491.75</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3206.16</v>
+        <v>3179.01</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>11708.03</v>
+        <v>11608.87</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3206.16</v>
+        <v>3179.01</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>8549.77</v>
+        <v>8477.360000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7481.05</v>
+        <v>7417.69</v>
       </c>
     </row>
     <row r="12">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>83360.27</v>
+        <v>82654.25999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3526.78</v>
+        <v>3496.91</v>
       </c>
     </row>
     <row r="14">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>5343.61</v>
+        <v>5298.35</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2671.8</v>
+        <v>2649.18</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>35267.81</v>
+        <v>34969.11</v>
       </c>
     </row>
     <row r="17">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>5841.08</v>
+        <v>5791.61</v>
       </c>
     </row>
     <row r="19">
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3206.16</v>
+        <v>3179.01</v>
       </c>
     </row>
     <row r="20">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4274.89</v>
+        <v>4238.68</v>
       </c>
     </row>
     <row r="21">
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2220.75</v>
+        <v>2201.94</v>
       </c>
     </row>
     <row r="22">
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>12824.66</v>
+        <v>12716.04</v>
       </c>
     </row>
     <row r="23">
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>10687.21</v>
+        <v>10596.7</v>
       </c>
     </row>
     <row r="24">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>2230.42</v>
+        <v>2211.53</v>
       </c>
     </row>
     <row r="25">
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>28855.48</v>
+        <v>28611.09</v>
       </c>
     </row>
     <row r="26">
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>3206.16</v>
+        <v>3179.01</v>
       </c>
     </row>
     <row r="27">
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>36336.53</v>
+        <v>36028.78</v>
       </c>
     </row>
     <row r="28">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>6604.7</v>
+        <v>6548.76</v>
       </c>
     </row>
     <row r="29">
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>17099.54</v>
+        <v>16954.72</v>
       </c>
     </row>
     <row r="30">
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>14962.1</v>
+        <v>14885.22</v>
       </c>
     </row>
     <row r="31">
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>15122.41</v>
+        <v>15044.71</v>
       </c>
     </row>
     <row r="32">
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>5011</v>
+        <v>4985.25</v>
       </c>
     </row>
     <row r="33">
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>3847.4</v>
+        <v>3827.63</v>
       </c>
     </row>
     <row r="34">
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>22004.97</v>
+        <v>21891.91</v>
       </c>
     </row>
     <row r="35">
@@ -2590,7 +2590,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3908.67</v>
+        <v>3888.58</v>
       </c>
     </row>
     <row r="36">
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>3847.4</v>
+        <v>3827.63</v>
       </c>
     </row>
     <row r="37">
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2351.19</v>
+        <v>2339.11</v>
       </c>
     </row>
     <row r="38">
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>10687.21</v>
+        <v>10632.3</v>
       </c>
     </row>
     <row r="39">
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>14962.1</v>
+        <v>14885.22</v>
       </c>
     </row>
     <row r="40">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>2244.32</v>
+        <v>2232.78</v>
       </c>
     </row>
     <row r="41">
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>6412.33</v>
+        <v>6379.38</v>
       </c>
     </row>
     <row r="42">
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>32061.64</v>
+        <v>31896.91</v>
       </c>
     </row>
     <row r="43">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>5343.61</v>
+        <v>5316.15</v>
       </c>
     </row>
     <row r="44">
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3206.16</v>
+        <v>3189.69</v>
       </c>
     </row>
     <row r="45">
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>26718.04</v>
+        <v>26580.76</v>
       </c>
     </row>
     <row r="46">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>7267.31</v>
+        <v>7229.97</v>
       </c>
     </row>
     <row r="47">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>4274.89</v>
+        <v>4252.92</v>
       </c>
     </row>
     <row r="48">
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>6932.23</v>
+        <v>6896.61</v>
       </c>
     </row>
     <row r="49">
@@ -3444,7 +3444,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3785.17</v>
+        <v>3765.72</v>
       </c>
     </row>
     <row r="50">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>4274.89</v>
+        <v>4252.92</v>
       </c>
     </row>
     <row r="51">
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2244.32</v>
+        <v>2232.78</v>
       </c>
     </row>
     <row r="52">
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2222.94</v>
+        <v>2211.52</v>
       </c>
     </row>
     <row r="53">
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>5290.17</v>
+        <v>5262.99</v>
       </c>
     </row>
     <row r="54">
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>10687.21</v>
+        <v>10632.3</v>
       </c>
     </row>
     <row r="55">
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>3206.16</v>
+        <v>3189.69</v>
       </c>
     </row>
     <row r="56">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>4809.25</v>
+        <v>4784.54</v>
       </c>
     </row>
     <row r="57">
@@ -3932,7 +3932,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>10687.21</v>
+        <v>10632.3</v>
       </c>
     </row>
     <row r="58">
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3206.16</v>
+        <v>3189.69</v>
       </c>
     </row>
     <row r="59">
@@ -4054,7 +4054,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1603.08</v>
+        <v>1594.85</v>
       </c>
     </row>
     <row r="60">
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>32061.64</v>
+        <v>31896.91</v>
       </c>
     </row>
     <row r="61">
@@ -4176,7 +4176,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>9404.75</v>
+        <v>9356.43</v>
       </c>
     </row>
     <row r="62">
@@ -4237,7 +4237,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2564.93</v>
+        <v>2551.75</v>
       </c>
     </row>
     <row r="63">
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>6412.33</v>
+        <v>6379.38</v>
       </c>
     </row>
     <row r="64">
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2244.32</v>
+        <v>2232.78</v>
       </c>
     </row>
     <row r="65">
@@ -4420,7 +4420,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>4561.74</v>
+        <v>4538.3</v>
       </c>
     </row>
     <row r="66">
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>3740.53</v>
+        <v>3721.31</v>
       </c>
     </row>
     <row r="67">
@@ -4542,7 +4542,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>24640.44</v>
+        <v>24513.84</v>
       </c>
     </row>
     <row r="68">
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2458.06</v>
+        <v>2445.43</v>
       </c>
     </row>
     <row r="69">
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>13893.38</v>
+        <v>13821.99</v>
       </c>
     </row>
     <row r="70">
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>16030.82</v>
+        <v>15948.45</v>
       </c>
     </row>
     <row r="71">
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>3206.16</v>
+        <v>3174.17</v>
       </c>
     </row>
     <row r="72">
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>17099.54</v>
+        <v>16928.89</v>
       </c>
     </row>
     <row r="73">
@@ -4908,7 +4908,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>3206.16</v>
+        <v>3174.17</v>
       </c>
     </row>
     <row r="74">
@@ -4969,7 +4969,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>8549.77</v>
+        <v>8464.440000000001</v>
       </c>
     </row>
     <row r="75">
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>41680.14</v>
+        <v>41264.16</v>
       </c>
     </row>
     <row r="76">
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2992.42</v>
+        <v>2962.56</v>
       </c>
     </row>
     <row r="77">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>3206.16</v>
+        <v>3174.17</v>
       </c>
     </row>
     <row r="78">
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>3740.53</v>
+        <v>3703.19</v>
       </c>
     </row>
     <row r="79">
@@ -5274,7 +5274,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>5343.61</v>
+        <v>5290.28</v>
       </c>
     </row>
     <row r="80">
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>13893.38</v>
+        <v>13754.72</v>
       </c>
     </row>
     <row r="81">
@@ -5396,7 +5396,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>9618.49</v>
+        <v>9522.5</v>
       </c>
     </row>
     <row r="82">
@@ -5457,7 +5457,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>6412.33</v>
+        <v>6348.33</v>
       </c>
     </row>
     <row r="83">
@@ -5518,7 +5518,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>18168.26</v>
+        <v>17986.94</v>
       </c>
     </row>
     <row r="84">
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>4274.89</v>
+        <v>4232.22</v>
       </c>
     </row>
     <row r="85">
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>5343.61</v>
+        <v>5290.28</v>
       </c>
     </row>
     <row r="86">
@@ -5701,7 +5701,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>35267.81</v>
+        <v>34915.83</v>
       </c>
     </row>
     <row r="87">
@@ -5762,7 +5762,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2230.42</v>
+        <v>2208.16</v>
       </c>
     </row>
     <row r="88">
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>3206.16</v>
+        <v>3174.17</v>
       </c>
     </row>
     <row r="89">
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>9084.129999999999</v>
+        <v>8993.469999999999</v>
       </c>
     </row>
     <row r="90">
@@ -5945,7 +5945,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>35267.81</v>
+        <v>34915.83</v>
       </c>
     </row>
     <row r="91">
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>14405.4</v>
+        <v>14261.63</v>
       </c>
     </row>
     <row r="92">
@@ -6067,7 +6067,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3740.53</v>
+        <v>3703.19</v>
       </c>
     </row>
     <row r="93">
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>2244.32</v>
+        <v>2221.92</v>
       </c>
     </row>
     <row r="94">
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>7481.05</v>
+        <v>7406.39</v>
       </c>
     </row>
     <row r="95">
@@ -6250,7 +6250,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>3206.16</v>
+        <v>3174.17</v>
       </c>
     </row>
     <row r="96">
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>4809.25</v>
+        <v>4761.25</v>
       </c>
     </row>
     <row r="97">
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>6412.33</v>
+        <v>6348.33</v>
       </c>
     </row>
     <row r="98">
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>44886.3</v>
+        <v>44438.33</v>
       </c>
     </row>
     <row r="99">
@@ -6494,7 +6494,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2491.85</v>
+        <v>2466.98</v>
       </c>
     </row>
     <row r="100">
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2244.32</v>
+        <v>2221.92</v>
       </c>
     </row>
     <row r="101">
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>4488.63</v>
+        <v>4443.83</v>
       </c>
     </row>
     <row r="102">
@@ -6677,7 +6677,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>21374.43</v>
+        <v>21150.59</v>
       </c>
     </row>
     <row r="103">
@@ -6738,7 +6738,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>3497.93</v>
+        <v>3461.29</v>
       </c>
     </row>
     <row r="104">
@@ -6799,7 +6799,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2244.32</v>
+        <v>2220.81</v>
       </c>
     </row>
     <row r="105">
@@ -6860,7 +6860,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2244.32</v>
+        <v>2220.81</v>
       </c>
     </row>
     <row r="106">
@@ -6921,7 +6921,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>3179.45</v>
+        <v>3146.15</v>
       </c>
     </row>
     <row r="107">
@@ -6982,7 +6982,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>2671.8</v>
+        <v>2643.82</v>
       </c>
     </row>
     <row r="108">
@@ -7043,7 +7043,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>17740.78</v>
+        <v>17554.99</v>
       </c>
     </row>
     <row r="109">
@@ -7104,7 +7104,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>9297.879999999999</v>
+        <v>9200.51</v>
       </c>
     </row>
     <row r="110">
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>2885.55</v>
+        <v>2855.33</v>
       </c>
     </row>
     <row r="111">
@@ -7226,7 +7226,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>3206.16</v>
+        <v>3172.59</v>
       </c>
     </row>
     <row r="112">
@@ -7287,7 +7287,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>2244.32</v>
+        <v>2220.81</v>
       </c>
     </row>
     <row r="113">
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2351.19</v>
+        <v>2326.57</v>
       </c>
     </row>
     <row r="114">
@@ -7409,7 +7409,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>7801.67</v>
+        <v>7719.97</v>
       </c>
     </row>
     <row r="115">
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>2671.8</v>
+        <v>2643.82</v>
       </c>
     </row>
     <row r="116">
@@ -7531,7 +7531,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>2229.63</v>
+        <v>2206.28</v>
       </c>
     </row>
     <row r="117">
@@ -7592,7 +7592,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>10687.21</v>
+        <v>10575.3</v>
       </c>
     </row>
     <row r="118">
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2244.32</v>
+        <v>2220.81</v>
       </c>
     </row>
     <row r="119">
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>11061.27</v>
+        <v>10945.43</v>
       </c>
     </row>
     <row r="120">
@@ -7775,7 +7775,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>2671.8</v>
+        <v>2643.82</v>
       </c>
     </row>
     <row r="121">
@@ -7836,7 +7836,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>16030.82</v>
+        <v>15862.94</v>
       </c>
     </row>
     <row r="122">
@@ -7897,7 +7897,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>7481.05</v>
+        <v>7402.71</v>
       </c>
     </row>
     <row r="123">
@@ -7958,7 +7958,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>7481.05</v>
+        <v>7402.71</v>
       </c>
     </row>
     <row r="124">
@@ -8019,7 +8019,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>24580.59</v>
+        <v>24323.18</v>
       </c>
     </row>
     <row r="125">
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>17099.54</v>
+        <v>16920.47</v>
       </c>
     </row>
     <row r="126">
@@ -8141,7 +8141,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>26718.04</v>
+        <v>26438.24</v>
       </c>
     </row>
     <row r="127">
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>6412.33</v>
+        <v>6345.18</v>
       </c>
     </row>
     <row r="128">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>3449.76</v>
+        <v>3413.64</v>
       </c>
     </row>
     <row r="129">
@@ -8324,7 +8324,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>6412.33</v>
+        <v>6345.18</v>
       </c>
     </row>
     <row r="130">
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>2244.32</v>
+        <v>2220.81</v>
       </c>
     </row>
     <row r="131">
@@ -8446,7 +8446,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>3380.84</v>
+        <v>3345.44</v>
       </c>
     </row>
     <row r="132">
@@ -8507,7 +8507,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2244.32</v>
+        <v>2220.81</v>
       </c>
     </row>
     <row r="133">
@@ -8568,7 +8568,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>2230.42</v>
+        <v>2207.06</v>
       </c>
     </row>
     <row r="134">
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>16030.82</v>
+        <v>15862.94</v>
       </c>
     </row>
     <row r="135">
@@ -8690,7 +8690,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>2244.32</v>
+        <v>2220.81</v>
       </c>
     </row>
     <row r="136">
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>3179.45</v>
+        <v>3146.15</v>
       </c>
     </row>
     <row r="137">
@@ -8812,7 +8812,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>3206.16</v>
+        <v>3172.59</v>
       </c>
     </row>
     <row r="138">
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2233.63</v>
+        <v>2210.24</v>
       </c>
     </row>
     <row r="139">
@@ -8934,7 +8934,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>3131.35</v>
+        <v>3098.56</v>
       </c>
     </row>
     <row r="140">
@@ -8995,7 +8995,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>7801.67</v>
+        <v>7719.97</v>
       </c>
     </row>
     <row r="141">
@@ -9056,7 +9056,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>3633.65</v>
+        <v>3613.79</v>
       </c>
     </row>
     <row r="142">
@@ -9117,7 +9117,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>10687.21</v>
+        <v>10628.8</v>
       </c>
     </row>
     <row r="143">
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>26718.04</v>
+        <v>26572</v>
       </c>
     </row>
     <row r="144">
@@ -9239,7 +9239,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>21630.92</v>
+        <v>21512.69</v>
       </c>
     </row>
     <row r="145">
@@ -9300,7 +9300,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>10872.86</v>
+        <v>10813.43</v>
       </c>
     </row>
     <row r="146">
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>4274.89</v>
+        <v>4251.52</v>
       </c>
     </row>
     <row r="147">
@@ -9422,7 +9422,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>11221.58</v>
+        <v>11160.24</v>
       </c>
     </row>
     <row r="148">
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>5343.61</v>
+        <v>5314.4</v>
       </c>
     </row>
     <row r="149">
@@ -9544,7 +9544,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>21374.43</v>
+        <v>21257.6</v>
       </c>
     </row>
     <row r="150">
@@ -9605,7 +9605,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2229.63</v>
+        <v>2217.44</v>
       </c>
     </row>
     <row r="151">
@@ -9666,7 +9666,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>35267.81</v>
+        <v>35075.04</v>
       </c>
     </row>
     <row r="152">
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>10152.85</v>
+        <v>10097.36</v>
       </c>
     </row>
     <row r="153">
@@ -9788,7 +9788,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>3206.16</v>
+        <v>3188.64</v>
       </c>
     </row>
     <row r="154">
@@ -9849,7 +9849,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>10687.21</v>
+        <v>10628.8</v>
       </c>
     </row>
     <row r="155">
@@ -9910,7 +9910,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>2244.32</v>
+        <v>2232.05</v>
       </c>
     </row>
     <row r="156">
@@ -9971,7 +9971,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>6696.34</v>
+        <v>6659.74</v>
       </c>
     </row>
     <row r="157">
@@ -10032,7 +10032,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>10687.21</v>
+        <v>10628.8</v>
       </c>
     </row>
     <row r="158">
@@ -10093,7 +10093,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>24580.59</v>
+        <v>24446.24</v>
       </c>
     </row>
     <row r="159">
@@ -10154,7 +10154,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>19236.99</v>
+        <v>19131.84</v>
       </c>
     </row>
     <row r="160">
@@ -10215,7 +10215,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>2671.8</v>
+        <v>2657.2</v>
       </c>
     </row>
     <row r="161">
@@ -10276,7 +10276,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>32061.64</v>
+        <v>31886.4</v>
       </c>
     </row>
     <row r="162">
@@ -10337,7 +10337,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>32061.64</v>
+        <v>31886.4</v>
       </c>
     </row>
     <row r="163">
@@ -10398,7 +10398,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>21374.43</v>
+        <v>21257.6</v>
       </c>
     </row>
     <row r="164">
@@ -10459,7 +10459,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>2800.05</v>
+        <v>2784.75</v>
       </c>
     </row>
     <row r="165">
@@ -10520,7 +10520,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>2244.32</v>
+        <v>2232.05</v>
       </c>
     </row>
     <row r="166">
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>2244.32</v>
+        <v>2232.05</v>
       </c>
     </row>
     <row r="167">
@@ -10642,7 +10642,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>2229.63</v>
+        <v>2217.44</v>
       </c>
     </row>
     <row r="168">
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>32061.64</v>
+        <v>31886.4</v>
       </c>
     </row>
     <row r="169">
@@ -10764,7 +10764,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>3206.16</v>
+        <v>3188.64</v>
       </c>
     </row>
     <row r="170">
@@ -10825,7 +10825,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>8816.950000000001</v>
+        <v>8768.76</v>
       </c>
     </row>
     <row r="171">
@@ -10886,7 +10886,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>8015.41</v>
+        <v>7971.6</v>
       </c>
     </row>
     <row r="172">
@@ -10947,7 +10947,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>3206.16</v>
+        <v>3188.64</v>
       </c>
     </row>
     <row r="173">
@@ -11008,7 +11008,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>3206.16</v>
+        <v>3188.64</v>
       </c>
     </row>
     <row r="174">
@@ -11069,7 +11069,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>2229.63</v>
+        <v>2217.44</v>
       </c>
     </row>
     <row r="175">
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>2671.8</v>
+        <v>2657.2</v>
       </c>
     </row>
     <row r="176">
@@ -11191,7 +11191,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>11007.47</v>
+        <v>10947.31</v>
       </c>
     </row>
     <row r="177">
@@ -11252,7 +11252,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>16030.82</v>
+        <v>15943.2</v>
       </c>
     </row>
     <row r="178">
@@ -11313,7 +11313,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>8229.16</v>
+        <v>8184.18</v>
       </c>
     </row>
     <row r="179">
@@ -11374,7 +11374,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>6412.33</v>
+        <v>6377.28</v>
       </c>
     </row>
     <row r="180">
@@ -11435,7 +11435,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>3206.16</v>
+        <v>3170.44</v>
       </c>
     </row>
     <row r="181">
@@ -11496,7 +11496,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>4809.25</v>
+        <v>4755.66</v>
       </c>
     </row>
     <row r="182">
@@ -11557,7 +11557,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>5343.61</v>
+        <v>5284.07</v>
       </c>
     </row>
     <row r="183">
@@ -11618,7 +11618,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>10687.21</v>
+        <v>10568.14</v>
       </c>
     </row>
     <row r="184">
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>5343.61</v>
+        <v>5284.07</v>
       </c>
     </row>
     <row r="185">
@@ -11740,7 +11740,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>3549.75</v>
+        <v>3510.2</v>
       </c>
     </row>
     <row r="186">
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>3398.53</v>
+        <v>3360.67</v>
       </c>
     </row>
     <row r="187">
@@ -11862,7 +11862,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>7481.05</v>
+        <v>7397.7</v>
       </c>
     </row>
     <row r="188">
@@ -11923,7 +11923,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>10687.21</v>
+        <v>10568.14</v>
       </c>
     </row>
     <row r="189">
@@ -11984,7 +11984,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>21374.43</v>
+        <v>21136.29</v>
       </c>
     </row>
     <row r="190">
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>21374.43</v>
+        <v>21136.29</v>
       </c>
     </row>
     <row r="191">
@@ -12106,7 +12106,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>6412.33</v>
+        <v>6340.89</v>
       </c>
     </row>
     <row r="192">
@@ -12167,7 +12167,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>3269.97</v>
+        <v>3233.53</v>
       </c>
     </row>
     <row r="193">
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>5343.61</v>
+        <v>5284.07</v>
       </c>
     </row>
     <row r="194">
@@ -12289,7 +12289,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>6412.33</v>
+        <v>6340.89</v>
       </c>
     </row>
     <row r="195">
@@ -12350,7 +12350,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>7481.05</v>
+        <v>7397.7</v>
       </c>
     </row>
     <row r="196">
@@ -12411,7 +12411,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>3206.16</v>
+        <v>3170.44</v>
       </c>
     </row>
     <row r="197">
@@ -12472,7 +12472,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>2244.32</v>
+        <v>2219.31</v>
       </c>
     </row>
     <row r="198">
@@ -12533,7 +12533,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>2778.68</v>
+        <v>2747.72</v>
       </c>
     </row>
     <row r="199">
@@ -12594,7 +12594,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>3306.62</v>
+        <v>3269.78</v>
       </c>
     </row>
     <row r="200">
@@ -12655,7 +12655,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>28855.48</v>
+        <v>28533.99</v>
       </c>
     </row>
     <row r="201">
@@ -12716,7 +12716,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>2229.89</v>
+        <v>2205.04</v>
       </c>
     </row>
     <row r="202">
@@ -12777,7 +12777,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>2233.63</v>
+        <v>2208.74</v>
       </c>
     </row>
     <row r="203">
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>10687.21</v>
+        <v>10568.14</v>
       </c>
     </row>
     <row r="204">
@@ -12899,7 +12899,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>2229.63</v>
+        <v>2204.79</v>
       </c>
     </row>
     <row r="205">
@@ -12960,7 +12960,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>36336.53</v>
+        <v>35931.69</v>
       </c>
     </row>
     <row r="206">
@@ -13021,7 +13021,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>2244.32</v>
+        <v>2219.31</v>
       </c>
     </row>
     <row r="207">
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>4577.93</v>
+        <v>4526.93</v>
       </c>
     </row>
     <row r="208">
@@ -13143,7 +13143,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>4568.38</v>
+        <v>4517.48</v>
       </c>
     </row>
     <row r="209">
@@ -13204,7 +13204,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>3206.16</v>
+        <v>3170.44</v>
       </c>
     </row>
     <row r="210">
@@ -13265,7 +13265,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>5343.61</v>
+        <v>5284.07</v>
       </c>
     </row>
     <row r="211">
@@ -13326,7 +13326,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>8549.77</v>
+        <v>8454.51</v>
       </c>
     </row>
     <row r="212">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>4274.89</v>
+        <v>4251.47</v>
       </c>
     </row>
     <row r="213">
@@ -13448,7 +13448,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>5984.84</v>
+        <v>5952.06</v>
       </c>
     </row>
     <row r="214">
@@ -13509,7 +13509,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>2738.77</v>
+        <v>2723.77</v>
       </c>
     </row>
     <row r="215">
@@ -13570,7 +13570,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>5343.61</v>
+        <v>5314.34</v>
       </c>
     </row>
     <row r="216">
@@ -13631,7 +13631,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>7068.53</v>
+        <v>7029.82</v>
       </c>
     </row>
     <row r="217">
@@ -13692,7 +13692,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>3740.53</v>
+        <v>3720.04</v>
       </c>
     </row>
     <row r="218">
@@ -13753,7 +13753,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>36309.38</v>
+        <v>36110.54</v>
       </c>
     </row>
     <row r="219">
@@ -13814,7 +13814,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>7171.12</v>
+        <v>7131.85</v>
       </c>
     </row>
     <row r="220">
@@ -13875,7 +13875,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>2244.32</v>
+        <v>2232.02</v>
       </c>
     </row>
     <row r="221">
@@ -13936,7 +13936,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>10687.21</v>
+        <v>10628.69</v>
       </c>
     </row>
     <row r="222">
@@ -13997,7 +13997,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>2244.32</v>
+        <v>2232.02</v>
       </c>
     </row>
     <row r="223">
@@ -14058,7 +14058,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>2244.32</v>
+        <v>2232.02</v>
       </c>
     </row>
     <row r="224">
@@ -14119,7 +14119,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>2244.32</v>
+        <v>2232.02</v>
       </c>
     </row>
     <row r="225">
@@ -14180,7 +14180,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>5639.91</v>
+        <v>5609.02</v>
       </c>
     </row>
     <row r="226">
@@ -14241,7 +14241,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>2229.63</v>
+        <v>2217.42</v>
       </c>
     </row>
     <row r="227">
@@ -14302,7 +14302,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>2229.63</v>
+        <v>2217.42</v>
       </c>
     </row>
     <row r="228">
@@ -14363,7 +14363,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>20369.83</v>
+        <v>20258.28</v>
       </c>
     </row>
     <row r="229">
@@ -14424,7 +14424,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>3740.53</v>
+        <v>3720.04</v>
       </c>
     </row>
     <row r="230">
@@ -14485,7 +14485,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>4695.96</v>
+        <v>4670.24</v>
       </c>
     </row>
     <row r="231">
@@ -14546,7 +14546,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>4532.48</v>
+        <v>4507.66</v>
       </c>
     </row>
     <row r="232">
@@ -14607,7 +14607,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>2229.63</v>
+        <v>2217.42</v>
       </c>
     </row>
     <row r="233">
@@ -14668,7 +14668,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>3206.16</v>
+        <v>3188.61</v>
       </c>
     </row>
     <row r="234">
@@ -14729,7 +14729,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>3206.16</v>
+        <v>3188.61</v>
       </c>
     </row>
     <row r="235">
@@ -14790,7 +14790,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>42748.86</v>
+        <v>42514.75</v>
       </c>
     </row>
     <row r="236">
@@ -14851,7 +14851,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>4488.63</v>
+        <v>4464.05</v>
       </c>
     </row>
     <row r="237">
@@ -14912,7 +14912,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>3206.16</v>
+        <v>3188.61</v>
       </c>
     </row>
     <row r="238">
@@ -14973,7 +14973,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>21374.43</v>
+        <v>21257.37</v>
       </c>
     </row>
     <row r="239">
@@ -15034,7 +15034,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>4999.48</v>
+        <v>4972.1</v>
       </c>
     </row>
     <row r="240">
@@ -15095,7 +15095,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>2229.63</v>
+        <v>2217.42</v>
       </c>
     </row>
     <row r="241">
@@ -15156,7 +15156,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>3206.16</v>
+        <v>3188.61</v>
       </c>
     </row>
     <row r="242">
@@ -15217,7 +15217,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>5343.61</v>
+        <v>5314.34</v>
       </c>
     </row>
     <row r="243">
@@ -15278,7 +15278,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>2864.06</v>
+        <v>2848.38</v>
       </c>
     </row>
     <row r="244">
@@ -15339,7 +15339,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>3527.98</v>
+        <v>3508.66</v>
       </c>
     </row>
     <row r="245">
@@ -15400,7 +15400,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>4274.89</v>
+        <v>4251.47</v>
       </c>
     </row>
     <row r="246">
@@ -15461,7 +15461,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>6412.33</v>
+        <v>6377.21</v>
       </c>
     </row>
     <row r="247">
@@ -15522,7 +15522,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>3729.84</v>
+        <v>3709.41</v>
       </c>
     </row>
     <row r="248">
@@ -15583,7 +15583,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>5343.61</v>
+        <v>5314.34</v>
       </c>
     </row>
     <row r="249">
@@ -15644,7 +15644,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>2244.32</v>
+        <v>2232.02</v>
       </c>
     </row>
     <row r="250">
@@ -15705,7 +15705,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>2244.32</v>
+        <v>2232.02</v>
       </c>
     </row>
     <row r="251">
@@ -15766,7 +15766,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>2233.63</v>
+        <v>2221.4</v>
       </c>
     </row>
     <row r="252">
@@ -15827,7 +15827,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>32061.64</v>
+        <v>31886.06</v>
       </c>
     </row>
     <row r="253">
@@ -15888,7 +15888,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>16030.82</v>
+        <v>15943.03</v>
       </c>
     </row>
     <row r="254">
@@ -15949,7 +15949,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>7481.05</v>
+        <v>7471.53</v>
       </c>
     </row>
     <row r="255">
@@ -16010,7 +16010,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>16030.82</v>
+        <v>16010.42</v>
       </c>
     </row>
     <row r="256">
@@ -16071,7 +16071,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>5343.61</v>
+        <v>5336.81</v>
       </c>
     </row>
     <row r="257">
@@ -16132,7 +16132,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>2229.63</v>
+        <v>2226.79</v>
       </c>
     </row>
     <row r="258">
@@ -16193,7 +16193,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>3206.16</v>
+        <v>3202.08</v>
       </c>
     </row>
     <row r="259">
@@ -16254,7 +16254,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>21374.43</v>
+        <v>21347.22</v>
       </c>
     </row>
     <row r="260">
@@ -16315,7 +16315,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>21374.43</v>
+        <v>21347.22</v>
       </c>
     </row>
     <row r="261">
@@ -16376,7 +16376,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>3206.16</v>
+        <v>3202.08</v>
       </c>
     </row>
     <row r="262">
@@ -16437,7 +16437,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>3206.16</v>
+        <v>3202.08</v>
       </c>
     </row>
     <row r="263">
@@ -16498,7 +16498,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>6412.33</v>
+        <v>6404.17</v>
       </c>
     </row>
     <row r="264">
@@ -16559,7 +16559,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>7781.13</v>
+        <v>7771.23</v>
       </c>
     </row>
     <row r="265">
@@ -16620,7 +16620,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>8015.41</v>
+        <v>8005.21</v>
       </c>
     </row>
     <row r="266">
@@ -16681,7 +16681,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>2230.42</v>
+        <v>2227.58</v>
       </c>
     </row>
     <row r="267">
@@ -16742,7 +16742,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>9661.24</v>
+        <v>9648.940000000001</v>
       </c>
     </row>
     <row r="268">
@@ -16803,7 +16803,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>10687.21</v>
+        <v>10673.61</v>
       </c>
     </row>
     <row r="269">
@@ -16864,7 +16864,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>32061.64</v>
+        <v>32020.83</v>
       </c>
     </row>
     <row r="270">
@@ -16925,7 +16925,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>12959.32</v>
+        <v>12942.82</v>
       </c>
     </row>
     <row r="271">
@@ -16986,7 +16986,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>6412.33</v>
+        <v>6404.17</v>
       </c>
     </row>
     <row r="272">
@@ -17047,7 +17047,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>4274.89</v>
+        <v>4269.44</v>
       </c>
     </row>
     <row r="273">
@@ -17108,7 +17108,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>4274.89</v>
+        <v>4269.44</v>
       </c>
     </row>
     <row r="274">
@@ -17169,7 +17169,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>2229.63</v>
+        <v>2226.79</v>
       </c>
     </row>
     <row r="275">
@@ -17230,7 +17230,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>5343.61</v>
+        <v>5336.81</v>
       </c>
     </row>
     <row r="276">
@@ -17291,7 +17291,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>5343.61</v>
+        <v>5336.81</v>
       </c>
     </row>
     <row r="277">
@@ -17352,7 +17352,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>3206.16</v>
+        <v>3202.08</v>
       </c>
     </row>
     <row r="278">
@@ -17413,7 +17413,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>3206.16</v>
+        <v>3202.08</v>
       </c>
     </row>
     <row r="279">
@@ -17474,7 +17474,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>3206.16</v>
+        <v>3202.08</v>
       </c>
     </row>
     <row r="280">
@@ -17535,7 +17535,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>6412.33</v>
+        <v>6404.17</v>
       </c>
     </row>
     <row r="281">
@@ -17596,7 +17596,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>26987.2</v>
+        <v>26952.85</v>
       </c>
     </row>
     <row r="282">
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>3206.16</v>
+        <v>3202.08</v>
       </c>
     </row>
     <row r="283">
@@ -17718,7 +17718,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>5343.61</v>
+        <v>5336.81</v>
       </c>
     </row>
     <row r="284">
@@ -17779,7 +17779,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>4274.89</v>
+        <v>4269.44</v>
       </c>
     </row>
     <row r="285">
@@ -17840,7 +17840,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>17099.54</v>
+        <v>17077.78</v>
       </c>
     </row>
     <row r="286">
@@ -17901,7 +17901,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>2233.63</v>
+        <v>2230.78</v>
       </c>
     </row>
     <row r="287">
@@ -17962,7 +17962,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>3740.53</v>
+        <v>3735.76</v>
       </c>
     </row>
     <row r="288">
@@ -18023,7 +18023,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>7267.31</v>
+        <v>7258.06</v>
       </c>
     </row>
     <row r="289">
@@ -18084,7 +18084,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>12821.84</v>
+        <v>12805.52</v>
       </c>
     </row>
     <row r="290">
@@ -18145,7 +18145,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>3344.45</v>
+        <v>3340.19</v>
       </c>
     </row>
     <row r="291">
@@ -18206,7 +18206,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>3344.45</v>
+        <v>3340.19</v>
       </c>
     </row>
     <row r="292">
@@ -18267,7 +18267,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>3206.16</v>
+        <v>3202.08</v>
       </c>
     </row>
     <row r="293">
@@ -18328,7 +18328,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>4407.41</v>
+        <v>4401.8</v>
       </c>
     </row>
     <row r="294">
@@ -18389,7 +18389,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>2671.8</v>
+        <v>2668.4</v>
       </c>
     </row>
     <row r="295">
@@ -18450,7 +18450,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>2244.32</v>
+        <v>2241.46</v>
       </c>
     </row>
     <row r="296">
@@ -18511,7 +18511,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>2244.32</v>
+        <v>2241.46</v>
       </c>
     </row>
     <row r="297">
@@ -18572,7 +18572,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>11755.94</v>
+        <v>11740.97</v>
       </c>
     </row>
     <row r="298">
@@ -18633,7 +18633,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>5343.61</v>
+        <v>5336.81</v>
       </c>
     </row>
     <row r="299">
@@ -18694,7 +18694,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>26718.04</v>
+        <v>26684.03</v>
       </c>
     </row>
     <row r="300">
@@ -18755,7 +18755,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>16030.82</v>
+        <v>16010.42</v>
       </c>
     </row>
     <row r="301">
@@ -18816,7 +18816,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>3206.16</v>
+        <v>3202.08</v>
       </c>
     </row>
     <row r="302">
@@ -18877,7 +18877,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>5343.61</v>
+        <v>5336.81</v>
       </c>
     </row>
     <row r="303">
@@ -18938,7 +18938,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>2346.06</v>
+        <v>2343.07</v>
       </c>
     </row>
     <row r="304">
@@ -18999,7 +18999,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>2244.32</v>
+        <v>2241.46</v>
       </c>
     </row>
     <row r="305">
@@ -19060,7 +19060,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>2671.8</v>
+        <v>2668.4</v>
       </c>
     </row>
     <row r="306">
@@ -19121,7 +19121,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>3740.53</v>
+        <v>3735.76</v>
       </c>
     </row>
     <row r="307">
@@ -19182,7 +19182,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>21374.43</v>
+        <v>21450.71</v>
       </c>
     </row>
     <row r="308">
@@ -19243,7 +19243,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>5343.61</v>
+        <v>5362.68</v>
       </c>
     </row>
     <row r="309">
@@ -19304,7 +19304,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>3206.16</v>
+        <v>3217.61</v>
       </c>
     </row>
     <row r="310">
@@ -19365,7 +19365,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>4168.01</v>
+        <v>4182.89</v>
       </c>
     </row>
     <row r="311">
@@ -19426,7 +19426,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>32061.64</v>
+        <v>32176.07</v>
       </c>
     </row>
     <row r="312">
@@ -19487,7 +19487,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>10687.21</v>
+        <v>10725.36</v>
       </c>
     </row>
     <row r="313">
@@ -19548,7 +19548,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>16030.82</v>
+        <v>16088.03</v>
       </c>
     </row>
     <row r="314">
@@ -19609,7 +19609,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>64123.29</v>
+        <v>64352.13</v>
       </c>
     </row>
     <row r="315">
@@ -19670,7 +19670,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>6412.33</v>
+        <v>6435.21</v>
       </c>
     </row>
     <row r="316">
@@ -19731,7 +19731,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>6412.33</v>
+        <v>6435.21</v>
       </c>
     </row>
     <row r="317">
@@ -19792,7 +19792,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>5343.61</v>
+        <v>5362.68</v>
       </c>
     </row>
     <row r="318">
@@ -19853,7 +19853,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>4274.89</v>
+        <v>4290.14</v>
       </c>
     </row>
     <row r="319">
@@ -19914,7 +19914,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>3206.16</v>
+        <v>3217.61</v>
       </c>
     </row>
     <row r="320">
@@ -19975,7 +19975,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>7801.67</v>
+        <v>7829.51</v>
       </c>
     </row>
     <row r="321">
@@ -20036,7 +20036,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>2244.32</v>
+        <v>2252.32</v>
       </c>
     </row>
     <row r="322">
@@ -20097,7 +20097,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>2233.63</v>
+        <v>2241.6</v>
       </c>
     </row>
     <row r="323">
@@ -20158,7 +20158,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>2244.32</v>
+        <v>2252.32</v>
       </c>
     </row>
     <row r="324">
@@ -20219,7 +20219,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>2458.06</v>
+        <v>2466.83</v>
       </c>
     </row>
     <row r="325">
@@ -20280,7 +20280,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>10687.21</v>
+        <v>10725.36</v>
       </c>
     </row>
     <row r="326">
@@ -20341,7 +20341,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>2233.63</v>
+        <v>2241.6</v>
       </c>
     </row>
     <row r="327">
@@ -20402,7 +20402,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>10687.21</v>
+        <v>10725.36</v>
       </c>
     </row>
     <row r="328">
@@ -20463,7 +20463,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>2778.68</v>
+        <v>2788.59</v>
       </c>
     </row>
     <row r="329">
@@ -20524,7 +20524,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>10687.21</v>
+        <v>10725.36</v>
       </c>
     </row>
     <row r="330">
@@ -20585,7 +20585,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>2244.32</v>
+        <v>2252.32</v>
       </c>
     </row>
     <row r="331">
@@ -20646,7 +20646,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>2351.19</v>
+        <v>2359.58</v>
       </c>
     </row>
     <row r="332">
@@ -20707,7 +20707,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>12290.3</v>
+        <v>12334.16</v>
       </c>
     </row>
     <row r="333">
@@ -20768,7 +20768,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>6412.33</v>
+        <v>6435.21</v>
       </c>
     </row>
     <row r="334">
@@ -20829,7 +20829,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>5343.61</v>
+        <v>5362.68</v>
       </c>
     </row>
     <row r="335">
@@ -20890,7 +20890,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>2220.75</v>
+        <v>2228.68</v>
       </c>
     </row>
     <row r="336">
@@ -20951,7 +20951,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>5343.61</v>
+        <v>5362.68</v>
       </c>
     </row>
     <row r="337">
@@ -21012,7 +21012,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>5450.48</v>
+        <v>5469.93</v>
       </c>
     </row>
     <row r="338">
@@ -21073,7 +21073,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>4274.89</v>
+        <v>4290.14</v>
       </c>
     </row>
     <row r="339">
@@ -21134,7 +21134,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>2244.32</v>
+        <v>2252.32</v>
       </c>
     </row>
     <row r="340">
@@ -21195,7 +21195,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>7481.05</v>
+        <v>7507.75</v>
       </c>
     </row>
     <row r="341">
@@ -21256,7 +21256,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>2244.32</v>
+        <v>2252.32</v>
       </c>
     </row>
     <row r="342">
@@ -21317,7 +21317,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>69466.89999999999</v>
+        <v>69714.81</v>
       </c>
     </row>
     <row r="343">
@@ -21378,7 +21378,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>2229.63</v>
+        <v>2237.59</v>
       </c>
     </row>
     <row r="344">
@@ -21439,7 +21439,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>4809.25</v>
+        <v>4826.41</v>
       </c>
     </row>
     <row r="345">
@@ -21500,7 +21500,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>5931.4</v>
+        <v>5952.57</v>
       </c>
     </row>
     <row r="346">
@@ -21561,7 +21561,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>34199.09</v>
+        <v>34321.14</v>
       </c>
     </row>
     <row r="347">
@@ -21622,7 +21622,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>10794.09</v>
+        <v>10832.61</v>
       </c>
     </row>
     <row r="348">
@@ -21683,7 +21683,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>10687.21</v>
+        <v>10725.36</v>
       </c>
     </row>
     <row r="349">
@@ -21744,7 +21744,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>9618.49</v>
+        <v>9652.82</v>
       </c>
     </row>
     <row r="350">
@@ -21805,7 +21805,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>10687.21</v>
+        <v>10725.36</v>
       </c>
     </row>
     <row r="351">
@@ -21866,7 +21866,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>4370.96</v>
+        <v>4386.56</v>
       </c>
     </row>
     <row r="352">
@@ -21927,7 +21927,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>21374.43</v>
+        <v>21450.71</v>
       </c>
     </row>
     <row r="353">
@@ -21988,7 +21988,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>14107.12</v>
+        <v>14157.47</v>
       </c>
     </row>
     <row r="354">
@@ -22049,7 +22049,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>5343.61</v>
+        <v>5362.68</v>
       </c>
     </row>
     <row r="355">
@@ -22110,7 +22110,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>4360.38</v>
+        <v>4375.95</v>
       </c>
     </row>
     <row r="356">
@@ -22171,7 +22171,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>5343.61</v>
+        <v>5362.68</v>
       </c>
     </row>
     <row r="357">
@@ -22232,7 +22232,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>4799.75</v>
+        <v>4851.95</v>
       </c>
     </row>
     <row r="358">
@@ -22293,7 +22293,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>2244.32</v>
+        <v>2268.73</v>
       </c>
     </row>
     <row r="359">
@@ -22354,7 +22354,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>2229.63</v>
+        <v>2253.88</v>
       </c>
     </row>
     <row r="360">
@@ -22415,7 +22415,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>8549.77</v>
+        <v>8642.76</v>
       </c>
     </row>
     <row r="361">
@@ -22476,7 +22476,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>2244.32</v>
+        <v>2268.73</v>
       </c>
     </row>
     <row r="362">
@@ -22537,7 +22537,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>2671.8</v>
+        <v>2700.86</v>
       </c>
     </row>
     <row r="363">
@@ -22598,7 +22598,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>3206.16</v>
+        <v>3241.04</v>
       </c>
     </row>
     <row r="364">
@@ -22659,7 +22659,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>5343.61</v>
+        <v>5401.73</v>
       </c>
     </row>
     <row r="365">
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>4632.91</v>
+        <v>4683.3</v>
       </c>
     </row>
     <row r="366">
@@ -22781,7 +22781,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>37364.21</v>
+        <v>37770.6</v>
       </c>
     </row>
     <row r="367">
@@ -22842,7 +22842,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>5343.61</v>
+        <v>5401.73</v>
       </c>
     </row>
     <row r="368">
@@ -22903,7 +22903,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>4809.25</v>
+        <v>4861.55</v>
       </c>
     </row>
     <row r="369">
@@ -22964,7 +22964,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>3206.16</v>
+        <v>3241.04</v>
       </c>
     </row>
     <row r="370">
@@ -23025,7 +23025,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>4274.89</v>
+        <v>4321.38</v>
       </c>
     </row>
     <row r="371">
@@ -23086,7 +23086,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>26678.49</v>
+        <v>26968.66</v>
       </c>
     </row>
     <row r="372">
@@ -23147,7 +23147,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>2613.52</v>
+        <v>2641.94</v>
       </c>
     </row>
     <row r="373">
@@ -23208,7 +23208,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>6952.5</v>
+        <v>7028.11</v>
       </c>
     </row>
     <row r="374">
@@ -23269,7 +23269,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>2244.32</v>
+        <v>2268.73</v>
       </c>
     </row>
     <row r="375">
@@ -23330,7 +23330,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>2244.32</v>
+        <v>2268.73</v>
       </c>
     </row>
     <row r="376">
@@ -23391,7 +23391,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>4274.89</v>
+        <v>4321.38</v>
       </c>
     </row>
     <row r="377">
@@ -23452,7 +23452,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>3206.16</v>
+        <v>3241.04</v>
       </c>
     </row>
     <row r="378">
@@ -23513,7 +23513,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>2244.32</v>
+        <v>2268.73</v>
       </c>
     </row>
     <row r="379">
@@ -23574,7 +23574,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>2244.32</v>
+        <v>2268.73</v>
       </c>
     </row>
     <row r="380">
@@ -23635,7 +23635,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>2229.63</v>
+        <v>2253.88</v>
       </c>
     </row>
     <row r="381">
@@ -23696,7 +23696,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>3740.53</v>
+        <v>3781.21</v>
       </c>
     </row>
     <row r="382">
@@ -23757,7 +23757,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>4809.25</v>
+        <v>4861.55</v>
       </c>
     </row>
     <row r="383">
@@ -23818,7 +23818,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>3206.16</v>
+        <v>3241.04</v>
       </c>
     </row>
     <row r="384">
@@ -23879,7 +23879,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>48092.47</v>
+        <v>48615.54</v>
       </c>
     </row>
     <row r="385">
@@ -23940,7 +23940,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>7630.67</v>
+        <v>7713.67</v>
       </c>
     </row>
     <row r="386">
@@ -24001,7 +24001,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>34199.09</v>
+        <v>34571.05</v>
       </c>
     </row>
     <row r="387">
@@ -24062,7 +24062,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>3206.16</v>
+        <v>3241.04</v>
       </c>
     </row>
     <row r="388">
@@ -24123,7 +24123,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>14962.1</v>
+        <v>15124.83</v>
       </c>
     </row>
     <row r="389">
@@ -24184,7 +24184,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>8122.28</v>
+        <v>8210.620000000001</v>
       </c>
     </row>
     <row r="390">
@@ -24245,7 +24245,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>6412.33</v>
+        <v>6482.07</v>
       </c>
     </row>
     <row r="391">
@@ -24306,7 +24306,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>2244.32</v>
+        <v>2268.73</v>
       </c>
     </row>
     <row r="392">
@@ -24367,7 +24367,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>4274.89</v>
+        <v>4321.38</v>
       </c>
     </row>
     <row r="393">
@@ -24428,7 +24428,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>5343.61</v>
+        <v>5361.18</v>
       </c>
     </row>
     <row r="394">
@@ -24489,7 +24489,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>7432.1</v>
+        <v>7456.55</v>
       </c>
     </row>
     <row r="395">
@@ -24550,7 +24550,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>7481.05</v>
+        <v>7505.66</v>
       </c>
     </row>
     <row r="396">
@@ -24611,7 +24611,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>8549.77</v>
+        <v>8577.889999999999</v>
       </c>
     </row>
     <row r="397">
@@ -24672,7 +24672,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>4274.89</v>
+        <v>4288.95</v>
       </c>
     </row>
     <row r="398">
@@ -24733,7 +24733,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>8549.77</v>
+        <v>8577.889999999999</v>
       </c>
     </row>
     <row r="399">
@@ -24794,7 +24794,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>22443.15</v>
+        <v>22516.97</v>
       </c>
     </row>
     <row r="400">
@@ -24855,7 +24855,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>16030.82</v>
+        <v>16083.55</v>
       </c>
     </row>
     <row r="401">
@@ -24916,7 +24916,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>4990.93</v>
+        <v>5007.34</v>
       </c>
     </row>
     <row r="402">
@@ -24977,7 +24977,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>5343.61</v>
+        <v>5361.18</v>
       </c>
     </row>
     <row r="403">
@@ -25038,7 +25038,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>2244.32</v>
+        <v>2251.7</v>
       </c>
     </row>
     <row r="404">
@@ -25099,7 +25099,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>2244.32</v>
+        <v>2251.7</v>
       </c>
     </row>
     <row r="405">
@@ -25160,7 +25160,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>21374.43</v>
+        <v>21444.73</v>
       </c>
     </row>
     <row r="406">
@@ -25221,7 +25221,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>2990.63</v>
+        <v>3000.47</v>
       </c>
     </row>
     <row r="407">
@@ -25282,7 +25282,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>2229.63</v>
+        <v>2236.96</v>
       </c>
     </row>
     <row r="408">
@@ -25343,7 +25343,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>33664.66</v>
+        <v>33775.38</v>
       </c>
     </row>
     <row r="409">
@@ -25404,7 +25404,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>2671.8</v>
+        <v>2680.59</v>
       </c>
     </row>
     <row r="410">
@@ -25465,7 +25465,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>2229.63</v>
+        <v>2236.96</v>
       </c>
     </row>
     <row r="411">
@@ -25526,7 +25526,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>21374.43</v>
+        <v>21444.73</v>
       </c>
     </row>
     <row r="412">
@@ -25587,7 +25587,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>7481.05</v>
+        <v>7505.66</v>
       </c>
     </row>
     <row r="413">
@@ -25648,7 +25648,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>2229.63</v>
+        <v>2236.96</v>
       </c>
     </row>
     <row r="414">
@@ -25709,7 +25709,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>2244.32</v>
+        <v>2251.7</v>
       </c>
     </row>
     <row r="415">
@@ -25770,7 +25770,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>5471.85</v>
+        <v>5489.85</v>
       </c>
     </row>
     <row r="416">
@@ -25831,7 +25831,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>6412.33</v>
+        <v>6433.42</v>
       </c>
     </row>
     <row r="417">
@@ -25892,7 +25892,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>4274.89</v>
+        <v>4288.95</v>
       </c>
     </row>
     <row r="418">
@@ -25953,7 +25953,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>6626.07</v>
+        <v>6647.87</v>
       </c>
     </row>
     <row r="419">
@@ -26014,7 +26014,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>10687.21</v>
+        <v>10722.37</v>
       </c>
     </row>
     <row r="420">
@@ -26075,7 +26075,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>24473.72</v>
+        <v>24554.22</v>
       </c>
     </row>
     <row r="421">
@@ -26136,7 +26136,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>2244.32</v>
+        <v>2251.7</v>
       </c>
     </row>
     <row r="422">
@@ -26197,7 +26197,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>2992.42</v>
+        <v>3002.26</v>
       </c>
     </row>
     <row r="423">
@@ -26258,7 +26258,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>4274.89</v>
+        <v>4288.95</v>
       </c>
     </row>
     <row r="424">
@@ -26319,7 +26319,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>53436.07</v>
+        <v>53611.83</v>
       </c>
     </row>
     <row r="425">
@@ -26380,7 +26380,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>8250.530000000001</v>
+        <v>8277.67</v>
       </c>
     </row>
     <row r="426">
@@ -26441,7 +26441,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>3206.16</v>
+        <v>3216.71</v>
       </c>
     </row>
     <row r="427">
@@ -26502,7 +26502,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>22443.15</v>
+        <v>22516.97</v>
       </c>
     </row>
     <row r="428">
@@ -26563,7 +26563,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>7801.67</v>
+        <v>7827.33</v>
       </c>
     </row>
     <row r="429">
@@ -26624,7 +26624,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>4916.12</v>
+        <v>4932.29</v>
       </c>
     </row>
     <row r="430">
@@ -26685,7 +26685,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>2244.32</v>
+        <v>2251.7</v>
       </c>
     </row>
     <row r="431">
@@ -26746,7 +26746,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>2351.19</v>
+        <v>2358.92</v>
       </c>
     </row>
     <row r="432">
@@ -26807,7 +26807,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>3740.53</v>
+        <v>3805.09</v>
       </c>
     </row>
     <row r="433">
@@ -26868,7 +26868,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>3313.04</v>
+        <v>3370.22</v>
       </c>
     </row>
     <row r="434">
@@ -26929,7 +26929,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>2244.32</v>
+        <v>2283.06</v>
       </c>
     </row>
     <row r="435">
@@ -26990,7 +26990,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>2992.42</v>
+        <v>3044.07</v>
       </c>
     </row>
     <row r="436">
@@ -27051,7 +27051,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>4274.89</v>
+        <v>4348.68</v>
       </c>
     </row>
     <row r="437">
@@ -27112,7 +27112,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>2351.19</v>
+        <v>2391.77</v>
       </c>
     </row>
     <row r="438">
@@ -27173,7 +27173,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>25435.57</v>
+        <v>25874.63</v>
       </c>
     </row>
     <row r="439">
@@ -27234,7 +27234,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>3206.16</v>
+        <v>3261.51</v>
       </c>
     </row>
     <row r="440">
@@ -27295,7 +27295,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>3206.16</v>
+        <v>3261.51</v>
       </c>
     </row>
     <row r="441">
@@ -27356,7 +27356,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>5343.61</v>
+        <v>5435.85</v>
       </c>
     </row>
     <row r="442">
@@ -27417,7 +27417,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>4766.49</v>
+        <v>4848.76</v>
       </c>
     </row>
     <row r="443">
@@ -27478,7 +27478,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>14962.1</v>
+        <v>15220.37</v>
       </c>
     </row>
     <row r="444">
@@ -27539,7 +27539,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>2272.98</v>
+        <v>2312.22</v>
       </c>
     </row>
     <row r="445">
@@ -27600,7 +27600,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>4274.89</v>
+        <v>4348.68</v>
       </c>
     </row>
     <row r="446">
@@ -27661,7 +27661,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>33429.9</v>
+        <v>34006.95</v>
       </c>
     </row>
     <row r="447">
@@ -27722,7 +27722,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>5343.61</v>
+        <v>5435.85</v>
       </c>
     </row>
     <row r="448">
@@ -27783,7 +27783,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>2351.19</v>
+        <v>2391.77</v>
       </c>
     </row>
     <row r="449">
@@ -27844,7 +27844,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>3206.16</v>
+        <v>3261.51</v>
       </c>
     </row>
     <row r="450">
@@ -27905,7 +27905,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>2229.63</v>
+        <v>2268.12</v>
       </c>
     </row>
     <row r="451">
@@ -27966,7 +27966,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>13893.38</v>
+        <v>14133.2</v>
       </c>
     </row>
     <row r="452">
@@ -28027,7 +28027,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>2244.32</v>
+        <v>2283.06</v>
       </c>
     </row>
     <row r="453">
@@ -28088,7 +28088,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>32061.64</v>
+        <v>32615.08</v>
       </c>
     </row>
     <row r="454">
@@ -28149,7 +28149,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>6412.33</v>
+        <v>6523.02</v>
       </c>
     </row>
     <row r="455">
@@ -28210,7 +28210,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>2841.04</v>
+        <v>2890.08</v>
       </c>
     </row>
     <row r="456">
@@ -28271,7 +28271,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>11221.58</v>
+        <v>11415.28</v>
       </c>
     </row>
     <row r="457">
@@ -28332,7 +28332,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>2244.32</v>
+        <v>2283.06</v>
       </c>
     </row>
     <row r="458">
@@ -28393,7 +28393,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>3206.16</v>
+        <v>3261.51</v>
       </c>
     </row>
     <row r="459">
@@ -28454,7 +28454,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>20840.07</v>
+        <v>21199.8</v>
       </c>
     </row>
     <row r="460">
@@ -28515,7 +28515,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>3242.03</v>
+        <v>3297.99</v>
       </c>
     </row>
     <row r="461">
@@ -28576,7 +28576,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>6412.33</v>
+        <v>6523.02</v>
       </c>
     </row>
     <row r="462">
@@ -28637,7 +28637,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>2244.32</v>
+        <v>2283.06</v>
       </c>
     </row>
     <row r="463">
@@ -28698,7 +28698,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>8015.41</v>
+        <v>8153.77</v>
       </c>
     </row>
     <row r="464">
@@ -28759,7 +28759,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>10687.21</v>
+        <v>10871.69</v>
       </c>
     </row>
     <row r="465">
@@ -28820,7 +28820,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>5343.61</v>
+        <v>5435.85</v>
       </c>
     </row>
     <row r="466">
@@ -28881,7 +28881,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>3740.53</v>
+        <v>3805.09</v>
       </c>
     </row>
     <row r="467">
@@ -28942,7 +28942,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>4274.89</v>
+        <v>4348.68</v>
       </c>
     </row>
     <row r="468">
@@ -29003,7 +29003,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>8549.77</v>
+        <v>8697.35</v>
       </c>
     </row>
     <row r="469">
@@ -29064,7 +29064,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>7053.56</v>
+        <v>7175.32</v>
       </c>
     </row>
     <row r="470">
@@ -29125,7 +29125,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>6946.69</v>
+        <v>7066.6</v>
       </c>
     </row>
     <row r="471">
@@ -29186,7 +29186,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>6412.33</v>
+        <v>6523.02</v>
       </c>
     </row>
     <row r="472">
@@ -29247,7 +29247,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>2671.8</v>
+        <v>2717.92</v>
       </c>
     </row>
     <row r="473">
@@ -29308,7 +29308,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>6412.33</v>
+        <v>6523.02</v>
       </c>
     </row>
     <row r="474">
@@ -29369,7 +29369,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>5343.61</v>
+        <v>5435.85</v>
       </c>
     </row>
     <row r="475">
@@ -29430,7 +29430,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>2244.32</v>
+        <v>2283.06</v>
       </c>
     </row>
     <row r="476">
@@ -29491,7 +29491,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>3206.16</v>
+        <v>3261.51</v>
       </c>
     </row>
     <row r="477">
@@ -29552,7 +29552,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>3206.16</v>
+        <v>3261.51</v>
       </c>
     </row>
     <row r="478">
@@ -29613,7 +29613,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>5343.61</v>
+        <v>5435.85</v>
       </c>
     </row>
     <row r="479">
@@ -29674,7 +29674,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>5343.61</v>
+        <v>5435.85</v>
       </c>
     </row>
     <row r="480">
@@ -29735,7 +29735,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>5343.61</v>
+        <v>5435.85</v>
       </c>
     </row>
     <row r="481">
@@ -29796,7 +29796,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>2244.32</v>
+        <v>2283.06</v>
       </c>
     </row>
     <row r="482">
@@ -29857,7 +29857,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>3045.86</v>
+        <v>3066.96</v>
       </c>
     </row>
     <row r="483">
@@ -29918,7 +29918,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>5343.61</v>
+        <v>5380.63</v>
       </c>
     </row>
     <row r="484">
@@ -29979,7 +29979,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>3932.89</v>
+        <v>3960.14</v>
       </c>
     </row>
     <row r="485">
@@ -30040,7 +30040,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>3206.16</v>
+        <v>3228.38</v>
       </c>
     </row>
     <row r="486">
@@ -30101,7 +30101,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>2244.32</v>
+        <v>2259.86</v>
       </c>
     </row>
     <row r="487">
@@ -30162,7 +30162,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>26718.04</v>
+        <v>26903.13</v>
       </c>
     </row>
     <row r="488">
@@ -30223,7 +30223,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>64123.29</v>
+        <v>64567.51</v>
       </c>
     </row>
     <row r="489">
@@ -30284,7 +30284,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>5343.61</v>
+        <v>5380.63</v>
       </c>
     </row>
     <row r="490">
@@ -30345,7 +30345,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>6412.33</v>
+        <v>6456.75</v>
       </c>
     </row>
     <row r="491">
@@ -30406,7 +30406,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>2244.32</v>
+        <v>2259.86</v>
       </c>
     </row>
     <row r="492">
@@ -30467,7 +30467,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>2229.63</v>
+        <v>2245.08</v>
       </c>
     </row>
     <row r="493">
@@ -30528,7 +30528,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>5343.61</v>
+        <v>5380.63</v>
       </c>
     </row>
     <row r="494">
@@ -30589,7 +30589,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>7481.05</v>
+        <v>7532.88</v>
       </c>
     </row>
     <row r="495">
@@ -30650,7 +30650,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>4274.89</v>
+        <v>4304.5</v>
       </c>
     </row>
     <row r="496">
@@ -30711,7 +30711,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>37405.25</v>
+        <v>37664.38</v>
       </c>
     </row>
     <row r="497">
@@ -30772,7 +30772,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>10687.21</v>
+        <v>10761.25</v>
       </c>
     </row>
     <row r="498">
@@ -30833,7 +30833,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>10687.21</v>
+        <v>10761.25</v>
       </c>
     </row>
     <row r="499">
@@ -30894,7 +30894,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>2244.32</v>
+        <v>2259.86</v>
       </c>
     </row>
     <row r="500">
@@ -30955,7 +30955,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>16030.82</v>
+        <v>16105.48</v>
       </c>
     </row>
     <row r="501">
@@ -31016,7 +31016,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>4499.32</v>
+        <v>4520.27</v>
       </c>
     </row>
     <row r="502">
@@ -31077,7 +31077,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>10687.21</v>
+        <v>10736.99</v>
       </c>
     </row>
     <row r="503">
@@ -31138,7 +31138,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>8549.77</v>
+        <v>8589.59</v>
       </c>
     </row>
     <row r="504">
@@ -31199,7 +31199,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>2671.8</v>
+        <v>2684.25</v>
       </c>
     </row>
     <row r="505">
@@ -31260,7 +31260,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>2671.8</v>
+        <v>2684.25</v>
       </c>
     </row>
     <row r="506">
@@ -31321,7 +31321,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>2244.32</v>
+        <v>2254.77</v>
       </c>
     </row>
     <row r="507">
@@ -31382,7 +31382,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>2671.8</v>
+        <v>2684.25</v>
       </c>
     </row>
     <row r="508">
@@ -31443,7 +31443,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>5877.97</v>
+        <v>5905.34</v>
       </c>
     </row>
     <row r="509">
@@ -31504,7 +31504,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>6412.33</v>
+        <v>6442.19</v>
       </c>
     </row>
     <row r="510">
@@ -31565,7 +31565,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>4512.56</v>
+        <v>4533.57</v>
       </c>
     </row>
     <row r="511">
@@ -31626,7 +31626,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>10687.21</v>
+        <v>10736.99</v>
       </c>
     </row>
     <row r="512">
@@ -31687,7 +31687,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>5343.61</v>
+        <v>5368.49</v>
       </c>
     </row>
     <row r="513">
@@ -31748,7 +31748,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>2618.37</v>
+        <v>2630.56</v>
       </c>
     </row>
     <row r="514">
@@ -31809,7 +31809,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>2244.32</v>
+        <v>2254.77</v>
       </c>
     </row>
     <row r="515">
@@ -31870,7 +31870,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>21374.43</v>
+        <v>21473.97</v>
       </c>
     </row>
     <row r="516">
@@ -31931,7 +31931,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>4068.3</v>
+        <v>4087.25</v>
       </c>
     </row>
     <row r="517">
@@ -31992,7 +31992,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>2458.06</v>
+        <v>2469.51</v>
       </c>
     </row>
     <row r="518">
@@ -32053,7 +32053,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>5343.61</v>
+        <v>5368.49</v>
       </c>
     </row>
     <row r="519">
@@ -32114,7 +32114,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>3367.11</v>
+        <v>3382.79</v>
       </c>
     </row>
     <row r="520">
@@ -32175,7 +32175,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>3588.68</v>
+        <v>3605.39</v>
       </c>
     </row>
     <row r="521">
@@ -32236,7 +32236,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>3206.16</v>
+        <v>3221.1</v>
       </c>
     </row>
     <row r="522">
@@ -32297,7 +32297,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>7481.05</v>
+        <v>7515.89</v>
       </c>
     </row>
     <row r="523">
@@ -32358,7 +32358,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>3206.16</v>
+        <v>3221.1</v>
       </c>
     </row>
     <row r="524">
@@ -32419,7 +32419,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>2244.32</v>
+        <v>2254.77</v>
       </c>
     </row>
     <row r="525">
@@ -32480,7 +32480,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>2671.8</v>
+        <v>2684.25</v>
       </c>
     </row>
     <row r="526">
@@ -32541,7 +32541,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>10687.21</v>
+        <v>10736.99</v>
       </c>
     </row>
     <row r="527">
@@ -32602,7 +32602,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>10687.21</v>
+        <v>10736.99</v>
       </c>
     </row>
     <row r="528">
@@ -32663,7 +32663,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>12823.93</v>
+        <v>12883.66</v>
       </c>
     </row>
     <row r="529">
@@ -32724,7 +32724,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>2874.41</v>
+        <v>2887.8</v>
       </c>
     </row>
     <row r="530">
@@ -32785,7 +32785,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>2229.63</v>
+        <v>2240.01</v>
       </c>
     </row>
     <row r="531">
@@ -32846,7 +32846,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>7481.05</v>
+        <v>7515.89</v>
       </c>
     </row>
     <row r="532">
@@ -32907,7 +32907,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>14427.74</v>
+        <v>14494.93</v>
       </c>
     </row>
     <row r="533">
@@ -32968,7 +32968,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>2244.32</v>
+        <v>2254.77</v>
       </c>
     </row>
     <row r="534">
@@ -33029,7 +33029,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>6412.33</v>
+        <v>6442.19</v>
       </c>
     </row>
     <row r="535">
@@ -33090,7 +33090,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>2297.7</v>
+        <v>2308.4</v>
       </c>
     </row>
     <row r="536">
@@ -33151,7 +33151,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>10687.21</v>
+        <v>10736.99</v>
       </c>
     </row>
     <row r="537">
@@ -33212,7 +33212,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>2244.32</v>
+        <v>2254.77</v>
       </c>
     </row>
     <row r="538">
@@ -33273,7 +33273,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>2244.32</v>
+        <v>2254.77</v>
       </c>
     </row>
     <row r="539">
@@ -33334,7 +33334,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>2297.75</v>
+        <v>2308.45</v>
       </c>
     </row>
     <row r="540">
@@ -33395,7 +33395,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>8015.41</v>
+        <v>8052.74</v>
       </c>
     </row>
     <row r="541">
@@ -33456,7 +33456,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>6412.33</v>
+        <v>6442.19</v>
       </c>
     </row>
     <row r="542">
@@ -33517,7 +33517,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>2229.63</v>
+        <v>2240.01</v>
       </c>
     </row>
     <row r="543">
@@ -33578,7 +33578,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>19629.21</v>
+        <v>19720.62</v>
       </c>
     </row>
     <row r="544">
@@ -33639,7 +33639,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>2670.73</v>
+        <v>2683.17</v>
       </c>
     </row>
     <row r="545">
@@ -33700,7 +33700,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>16030.82</v>
+        <v>16105.48</v>
       </c>
     </row>
     <row r="546">
@@ -33761,7 +33761,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>4809.25</v>
+        <v>4831.64</v>
       </c>
     </row>
     <row r="547">
@@ -33822,7 +33822,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>10687.21</v>
+        <v>10736.99</v>
       </c>
     </row>
     <row r="548">
@@ -33883,7 +33883,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>14962.1</v>
+        <v>15031.78</v>
       </c>
     </row>
     <row r="549">
@@ -33944,7 +33944,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>30992.92</v>
+        <v>31137.26</v>
       </c>
     </row>
     <row r="550">
@@ -34005,7 +34005,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>2244.32</v>
+        <v>2260.5</v>
       </c>
     </row>
     <row r="551">
@@ -34066,7 +34066,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>2244.32</v>
+        <v>2260.5</v>
       </c>
     </row>
     <row r="552">
@@ -34127,7 +34127,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>3206.16</v>
+        <v>3229.28</v>
       </c>
     </row>
     <row r="553">
@@ -34188,7 +34188,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>14962.1</v>
+        <v>15069.97</v>
       </c>
     </row>
     <row r="554">
@@ -34249,7 +34249,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>18382.01</v>
+        <v>18514.53</v>
       </c>
     </row>
     <row r="555">
@@ -34310,7 +34310,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>7706.6</v>
+        <v>7762.16</v>
       </c>
     </row>
     <row r="556">
@@ -34371,7 +34371,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>2671.8</v>
+        <v>2691.07</v>
       </c>
     </row>
     <row r="557">
@@ -34432,7 +34432,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>3740.53</v>
+        <v>3767.49</v>
       </c>
     </row>
     <row r="558">
@@ -34493,7 +34493,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>6132.63</v>
+        <v>6176.84</v>
       </c>
     </row>
     <row r="559">
@@ -34554,7 +34554,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>5343.61</v>
+        <v>5382.13</v>
       </c>
     </row>
     <row r="560">
@@ -34615,7 +34615,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>21374.43</v>
+        <v>21528.53</v>
       </c>
     </row>
     <row r="561">
@@ -34676,7 +34676,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>10067.41</v>
+        <v>10139.99</v>
       </c>
     </row>
     <row r="562">
@@ -34737,7 +34737,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>10687.21</v>
+        <v>10764.26</v>
       </c>
     </row>
     <row r="563">
@@ -34798,7 +34798,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>4103.89</v>
+        <v>4133.48</v>
       </c>
     </row>
     <row r="564">
@@ -34859,7 +34859,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>7481.05</v>
+        <v>7534.98</v>
       </c>
     </row>
     <row r="565">
@@ -34920,7 +34920,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>4953.16</v>
+        <v>4988.87</v>
       </c>
     </row>
     <row r="566">
@@ -34981,7 +34981,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>5259.32</v>
+        <v>5297.23</v>
       </c>
     </row>
     <row r="567">
@@ -35042,7 +35042,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>3042.52</v>
+        <v>3064.45</v>
       </c>
     </row>
     <row r="568">
@@ -35103,7 +35103,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>2671.8</v>
+        <v>2691.07</v>
       </c>
     </row>
     <row r="569">
@@ -35164,7 +35164,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>5877.97</v>
+        <v>5920.34</v>
       </c>
     </row>
     <row r="570">
@@ -35225,7 +35225,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>8549.77</v>
+        <v>8611.41</v>
       </c>
     </row>
     <row r="571">
@@ -35286,7 +35286,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>32061.64</v>
+        <v>32292.79</v>
       </c>
     </row>
     <row r="572">
@@ -35347,7 +35347,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>16030.82</v>
+        <v>16146.39</v>
       </c>
     </row>
     <row r="573">
@@ -35408,7 +35408,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>4274.89</v>
+        <v>4305.71</v>
       </c>
     </row>
     <row r="574">
@@ -35469,7 +35469,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>8015.41</v>
+        <v>8073.2</v>
       </c>
     </row>
     <row r="575">
@@ -35530,7 +35530,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>6412.33</v>
+        <v>6458.56</v>
       </c>
     </row>
     <row r="576">
@@ -35591,7 +35591,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>8549.77</v>
+        <v>8611.41</v>
       </c>
     </row>
     <row r="577">
@@ -35652,7 +35652,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>10687.21</v>
+        <v>10764.26</v>
       </c>
     </row>
     <row r="578">
@@ -35713,7 +35713,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>5343.61</v>
+        <v>5382.13</v>
       </c>
     </row>
     <row r="579">
@@ -35774,7 +35774,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>3163.42</v>
+        <v>3186.22</v>
       </c>
     </row>
     <row r="580">
@@ -35835,7 +35835,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>2671.8</v>
+        <v>2691.07</v>
       </c>
     </row>
     <row r="581">
@@ -35896,7 +35896,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>6412.33</v>
+        <v>6458.56</v>
       </c>
     </row>
     <row r="582">
@@ -35957,7 +35957,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>2244.32</v>
+        <v>2260.5</v>
       </c>
     </row>
     <row r="583">
@@ -36018,7 +36018,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>28855.48</v>
+        <v>29063.51</v>
       </c>
     </row>
     <row r="584">
@@ -36079,7 +36079,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>3206.16</v>
+        <v>3229.28</v>
       </c>
     </row>
     <row r="585">
@@ -36140,7 +36140,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>2671.8</v>
+        <v>2691.07</v>
       </c>
     </row>
     <row r="586">
@@ -36201,7 +36201,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>5343.61</v>
+        <v>5382.13</v>
       </c>
     </row>
     <row r="587">
@@ -36262,7 +36262,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>52109.55</v>
+        <v>52485.23</v>
       </c>
     </row>
     <row r="588">
@@ -36323,7 +36323,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>2671.8</v>
+        <v>2691.07</v>
       </c>
     </row>
     <row r="589">
@@ -36384,7 +36384,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>2284.93</v>
+        <v>2301.4</v>
       </c>
     </row>
     <row r="590">
@@ -36445,7 +36445,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>7481.05</v>
+        <v>7534.98</v>
       </c>
     </row>
     <row r="591">
@@ -36506,7 +36506,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>3206.16</v>
+        <v>3229.28</v>
       </c>
     </row>
     <row r="592">
@@ -36567,7 +36567,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>16030.82</v>
+        <v>16146.39</v>
       </c>
     </row>
     <row r="593">
@@ -36628,7 +36628,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>6412.33</v>
+        <v>6458.56</v>
       </c>
     </row>
     <row r="594">
@@ -36689,7 +36689,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>2671.8</v>
+        <v>2691.07</v>
       </c>
     </row>
     <row r="595">
@@ -36750,7 +36750,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>4071.94</v>
+        <v>4101.29</v>
       </c>
     </row>
     <row r="596">
@@ -36811,7 +36811,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>3740.53</v>
+        <v>3767.49</v>
       </c>
     </row>
     <row r="597">
@@ -36872,7 +36872,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>21374.43</v>
+        <v>21528.53</v>
       </c>
     </row>
     <row r="598">
@@ -36933,7 +36933,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>2244.32</v>
+        <v>2260.5</v>
       </c>
     </row>
     <row r="599">
@@ -36994,7 +36994,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>37084.63</v>
+        <v>37351.99</v>
       </c>
     </row>
     <row r="600">
@@ -37055,7 +37055,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>4551.49</v>
+        <v>4584.3</v>
       </c>
     </row>
     <row r="601">
@@ -37116,7 +37116,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>9618.49</v>
+        <v>9601.43</v>
       </c>
     </row>
     <row r="602">
@@ -37177,7 +37177,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>35267.81</v>
+        <v>35205.26</v>
       </c>
     </row>
     <row r="603">
@@ -37238,7 +37238,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>2244.32</v>
+        <v>2240.33</v>
       </c>
     </row>
     <row r="604">
@@ -37299,7 +37299,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>3206.16</v>
+        <v>3200.48</v>
       </c>
     </row>
     <row r="605">
@@ -37360,7 +37360,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>8447.450000000001</v>
+        <v>8432.459999999999</v>
       </c>
     </row>
     <row r="606">
@@ -37421,7 +37421,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>5343.61</v>
+        <v>5334.13</v>
       </c>
     </row>
     <row r="607">
@@ -37482,7 +37482,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>5343.61</v>
+        <v>5334.13</v>
       </c>
     </row>
     <row r="608">
@@ -37543,7 +37543,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>2233.63</v>
+        <v>2229.67</v>
       </c>
     </row>
     <row r="609">
@@ -37604,7 +37604,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>13893.38</v>
+        <v>13868.74</v>
       </c>
     </row>
     <row r="610">
@@ -37665,7 +37665,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>6412.33</v>
+        <v>6400.96</v>
       </c>
     </row>
     <row r="611">
@@ -37726,7 +37726,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>10259.73</v>
+        <v>10241.53</v>
       </c>
     </row>
     <row r="612">
@@ -37787,7 +37787,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>6255.23</v>
+        <v>6244.13</v>
       </c>
     </row>
     <row r="613">
@@ -37848,7 +37848,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>2229.63</v>
+        <v>2225.68</v>
       </c>
     </row>
     <row r="614">
@@ -37909,7 +37909,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>18892.3</v>
+        <v>18858.79</v>
       </c>
     </row>
     <row r="615">
@@ -37970,7 +37970,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>2244.32</v>
+        <v>2240.33</v>
       </c>
     </row>
     <row r="616">
@@ -38031,7 +38031,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>7481.05</v>
+        <v>7467.78</v>
       </c>
     </row>
     <row r="617">
@@ -38092,7 +38092,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>4274.89</v>
+        <v>4267.3</v>
       </c>
     </row>
     <row r="618">
@@ -38153,7 +38153,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>2244.32</v>
+        <v>2240.33</v>
       </c>
     </row>
     <row r="619">
@@ -38214,7 +38214,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>4274.89</v>
+        <v>4267.3</v>
       </c>
     </row>
     <row r="620">
@@ -38275,7 +38275,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>73577.82000000001</v>
+        <v>73447.32000000001</v>
       </c>
     </row>
     <row r="621">
@@ -38336,7 +38336,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>4809.25</v>
+        <v>4800.72</v>
       </c>
     </row>
     <row r="622">
@@ -38397,7 +38397,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>3076.14</v>
+        <v>3070.68</v>
       </c>
     </row>
     <row r="623">
@@ -38458,7 +38458,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>2244.32</v>
+        <v>2240.33</v>
       </c>
     </row>
     <row r="624">
@@ -38519,7 +38519,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>4274.89</v>
+        <v>4267.3</v>
       </c>
     </row>
     <row r="625">
@@ -38580,7 +38580,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>2409.97</v>
+        <v>2405.69</v>
       </c>
     </row>
     <row r="626">
@@ -38641,7 +38641,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>8549.77</v>
+        <v>8534.610000000001</v>
       </c>
     </row>
     <row r="627">
@@ -38702,7 +38702,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>2230.42</v>
+        <v>2226.47</v>
       </c>
     </row>
     <row r="628">
@@ -38763,7 +38763,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>21374.43</v>
+        <v>21336.52</v>
       </c>
     </row>
     <row r="629">
@@ -38824,7 +38824,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>44886.3</v>
+        <v>44806.69</v>
       </c>
     </row>
     <row r="630">
@@ -38885,7 +38885,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>37405.25</v>
+        <v>37338.91</v>
       </c>
     </row>
     <row r="631">
@@ -38946,7 +38946,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>4274.89</v>
+        <v>4267.3</v>
       </c>
     </row>
     <row r="632">
@@ -39007,7 +39007,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>2869.52</v>
+        <v>2864.43</v>
       </c>
     </row>
     <row r="633">
@@ -39068,7 +39068,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>8788.68</v>
+        <v>8773.09</v>
       </c>
     </row>
     <row r="634">
@@ -39129,7 +39129,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>4274.89</v>
+        <v>4267.3</v>
       </c>
     </row>
     <row r="635">
@@ -39190,7 +39190,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>14962.1</v>
+        <v>14935.56</v>
       </c>
     </row>
     <row r="636">
@@ -39251,7 +39251,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>5877.97</v>
+        <v>5867.54</v>
       </c>
     </row>
     <row r="637">
@@ -39312,7 +39312,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>3206.16</v>
+        <v>3200.48</v>
       </c>
     </row>
     <row r="638">
@@ -39373,7 +39373,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>3198.15</v>
+        <v>3192.48</v>
       </c>
     </row>
     <row r="639">
@@ -39434,7 +39434,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>6052.25</v>
+        <v>6041.51</v>
       </c>
     </row>
     <row r="640">
@@ -39495,7 +39495,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>5343.61</v>
+        <v>5321.58</v>
       </c>
     </row>
     <row r="641">
@@ -39556,7 +39556,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>2521.17</v>
+        <v>2510.78</v>
       </c>
     </row>
     <row r="642">
@@ -39617,7 +39617,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>2671.8</v>
+        <v>2660.79</v>
       </c>
     </row>
     <row r="643">
@@ -39678,7 +39678,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>2230.42</v>
+        <v>2221.23</v>
       </c>
     </row>
     <row r="644">
@@ -39739,7 +39739,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>7481.05</v>
+        <v>7450.22</v>
       </c>
     </row>
     <row r="645">
@@ -39800,7 +39800,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>4274.89</v>
+        <v>4257.27</v>
       </c>
     </row>
     <row r="646">
@@ -39861,7 +39861,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>2229.63</v>
+        <v>2220.44</v>
       </c>
     </row>
     <row r="647">
@@ -39922,7 +39922,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>5343.61</v>
+        <v>5321.58</v>
       </c>
     </row>
     <row r="648">
@@ -39983,7 +39983,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>3206.16</v>
+        <v>3192.95</v>
       </c>
     </row>
     <row r="649">
@@ -40044,7 +40044,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>6412.33</v>
+        <v>6385.9</v>
       </c>
     </row>
     <row r="650">
@@ -40105,7 +40105,7 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>2351.19</v>
+        <v>2341.5</v>
       </c>
     </row>
     <row r="651">
@@ -40166,7 +40166,7 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>5343.61</v>
+        <v>5321.58</v>
       </c>
     </row>
     <row r="652">
@@ -40227,7 +40227,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>2229.63</v>
+        <v>2220.44</v>
       </c>
     </row>
     <row r="653">
@@ -40288,7 +40288,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>20733.2</v>
+        <v>20647.74</v>
       </c>
     </row>
     <row r="654">
@@ -40349,7 +40349,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>12824.66</v>
+        <v>12771.8</v>
       </c>
     </row>
     <row r="655">
@@ -40410,7 +40410,7 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>5343.61</v>
+        <v>5321.58</v>
       </c>
     </row>
     <row r="656">
@@ -40471,7 +40471,7 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>21374.43</v>
+        <v>21286.33</v>
       </c>
     </row>
     <row r="657">
@@ -40532,7 +40532,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>7481.05</v>
+        <v>7450.22</v>
       </c>
     </row>
     <row r="658">
@@ -40593,7 +40593,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>2244.32</v>
+        <v>2235.06</v>
       </c>
     </row>
     <row r="659">
@@ -40654,7 +40654,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>2351.19</v>
+        <v>2341.5</v>
       </c>
     </row>
     <row r="660">
@@ -40715,7 +40715,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>2351.19</v>
+        <v>2341.5</v>
       </c>
     </row>
     <row r="661">
@@ -40776,7 +40776,7 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>9618.49</v>
+        <v>9578.85</v>
       </c>
     </row>
     <row r="662">
@@ -40837,7 +40837,7 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>34199.09</v>
+        <v>34058.13</v>
       </c>
     </row>
     <row r="663">
@@ -40898,7 +40898,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>5237.21</v>
+        <v>5215.62</v>
       </c>
     </row>
     <row r="664">
@@ -40959,7 +40959,7 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>2967.93</v>
+        <v>2955.7</v>
       </c>
     </row>
     <row r="665">
@@ -41020,7 +41020,7 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>3206.16</v>
+        <v>3192.95</v>
       </c>
     </row>
     <row r="666">
@@ -41081,7 +41081,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>3143.11</v>
+        <v>3130.16</v>
       </c>
     </row>
     <row r="667">
@@ -41142,7 +41142,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>2244.32</v>
+        <v>2235.06</v>
       </c>
     </row>
     <row r="668">
@@ -41203,7 +41203,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>16030.82</v>
+        <v>15964.75</v>
       </c>
     </row>
     <row r="669">
@@ -41264,7 +41264,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>5594.76</v>
+        <v>5571.7</v>
       </c>
     </row>
     <row r="670">
@@ -41325,7 +41325,7 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>2458.06</v>
+        <v>2447.93</v>
       </c>
     </row>
     <row r="671">
@@ -41386,7 +41386,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>16030.82</v>
+        <v>15964.75</v>
       </c>
     </row>
     <row r="672">
@@ -41447,7 +41447,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>2244.32</v>
+        <v>2235.06</v>
       </c>
     </row>
     <row r="673">
@@ -41508,7 +41508,7 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>21374.43</v>
+        <v>21286.33</v>
       </c>
     </row>
     <row r="674">
@@ -41569,7 +41569,7 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>2671.8</v>
+        <v>2660.79</v>
       </c>
     </row>
     <row r="675">
@@ -41630,7 +41630,7 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>2244.32</v>
+        <v>2235.06</v>
       </c>
     </row>
     <row r="676">
@@ -41691,7 +41691,7 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>3206.16</v>
+        <v>3192.95</v>
       </c>
     </row>
     <row r="677">
@@ -41752,7 +41752,7 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>21374.43</v>
+        <v>21286.33</v>
       </c>
     </row>
     <row r="678">
@@ -41813,7 +41813,7 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>2229.63</v>
+        <v>2220.44</v>
       </c>
     </row>
     <row r="679">
@@ -41874,7 +41874,7 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>31634.16</v>
+        <v>31503.77</v>
       </c>
     </row>
     <row r="680">
@@ -41935,7 +41935,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>15389.59</v>
+        <v>15326.16</v>
       </c>
     </row>
     <row r="681">
@@ -41996,7 +41996,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>2244.32</v>
+        <v>2235.06</v>
       </c>
     </row>
     <row r="682">
@@ -42057,7 +42057,7 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>2244.32</v>
+        <v>2235.06</v>
       </c>
     </row>
     <row r="683">
@@ -42118,7 +42118,7 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>21374.43</v>
+        <v>21341.3</v>
       </c>
     </row>
     <row r="684">
@@ -42179,7 +42179,7 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>10687.21</v>
+        <v>10670.65</v>
       </c>
     </row>
     <row r="685">
@@ -42240,7 +42240,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>2671.8</v>
+        <v>2667.66</v>
       </c>
     </row>
     <row r="686">
@@ -42301,7 +42301,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>5343.61</v>
+        <v>5335.33</v>
       </c>
     </row>
     <row r="687">
@@ -42362,7 +42362,7 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>6412.33</v>
+        <v>6402.39</v>
       </c>
     </row>
     <row r="688">
@@ -42423,7 +42423,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>3206.16</v>
+        <v>3201.2</v>
       </c>
     </row>
     <row r="689">
@@ -42484,7 +42484,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>16030.82</v>
+        <v>16005.98</v>
       </c>
     </row>
     <row r="690">
@@ -42545,7 +42545,7 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>7694.79</v>
+        <v>7682.87</v>
       </c>
     </row>
     <row r="691">
@@ -42606,7 +42606,7 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>4274.89</v>
+        <v>4268.26</v>
       </c>
     </row>
     <row r="692">
@@ -42667,7 +42667,7 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>5343.61</v>
+        <v>5335.33</v>
       </c>
     </row>
     <row r="693">
@@ -42728,7 +42728,7 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>8549.77</v>
+        <v>8536.52</v>
       </c>
     </row>
     <row r="694">
@@ -42789,7 +42789,7 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>5343.61</v>
+        <v>5335.33</v>
       </c>
     </row>
     <row r="695">
@@ -42850,7 +42850,7 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>39542.69</v>
+        <v>39481.41</v>
       </c>
     </row>
     <row r="696">
@@ -42911,7 +42911,7 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>4146.64</v>
+        <v>4140.21</v>
       </c>
     </row>
     <row r="697">
@@ -42972,7 +42972,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>73528.03999999999</v>
+        <v>73414.07000000001</v>
       </c>
     </row>
     <row r="698">
@@ -43033,7 +43033,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>32061.64</v>
+        <v>32011.95</v>
       </c>
     </row>
     <row r="699">
@@ -43094,7 +43094,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>2266.76</v>
+        <v>2263.24</v>
       </c>
     </row>
     <row r="700">
@@ -43155,7 +43155,7 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>5343.61</v>
+        <v>5335.33</v>
       </c>
     </row>
     <row r="701">
@@ -43216,7 +43216,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>10687.21</v>
+        <v>10670.65</v>
       </c>
     </row>
     <row r="702">
@@ -43277,7 +43277,7 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>10687.21</v>
+        <v>10670.65</v>
       </c>
     </row>
     <row r="703">
@@ -43338,7 +43338,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>4998.43</v>
+        <v>4990.68</v>
       </c>
     </row>
     <row r="704">
@@ -43399,7 +43399,7 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>2671.8</v>
+        <v>2667.66</v>
       </c>
     </row>
     <row r="705">
@@ -43460,7 +43460,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>2244.32</v>
+        <v>2240.84</v>
       </c>
     </row>
     <row r="706">
@@ -43521,7 +43521,7 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>2244.32</v>
+        <v>2240.84</v>
       </c>
     </row>
     <row r="707">
@@ -43582,7 +43582,7 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>14000.25</v>
+        <v>13978.55</v>
       </c>
     </row>
     <row r="708">
@@ -43643,7 +43643,7 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>2817.54</v>
+        <v>2813.17</v>
       </c>
     </row>
     <row r="709">
@@ -43704,7 +43704,7 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>5343.61</v>
+        <v>5335.33</v>
       </c>
     </row>
     <row r="710">
@@ -43765,7 +43765,7 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>16030.82</v>
+        <v>16005.98</v>
       </c>
     </row>
     <row r="711">
@@ -43826,7 +43826,7 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>2244.32</v>
+        <v>2240.84</v>
       </c>
     </row>
     <row r="712">
@@ -43887,7 +43887,7 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>3206.16</v>
+        <v>3201.2</v>
       </c>
     </row>
     <row r="713">
@@ -43948,7 +43948,7 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>15431.44</v>
+        <v>15407.52</v>
       </c>
     </row>
     <row r="714">
@@ -44009,7 +44009,7 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>5771.1</v>
+        <v>5762.15</v>
       </c>
     </row>
     <row r="715">
@@ -44070,7 +44070,7 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>3206.16</v>
+        <v>3201.2</v>
       </c>
     </row>
     <row r="716">
@@ -44131,7 +44131,7 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>3740.53</v>
+        <v>3734.73</v>
       </c>
     </row>
     <row r="717">
@@ -44192,7 +44192,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>3206.16</v>
+        <v>3201.2</v>
       </c>
     </row>
     <row r="718">
@@ -44253,7 +44253,7 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>2244.32</v>
+        <v>2240.84</v>
       </c>
     </row>
     <row r="719">
@@ -44314,7 +44314,7 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>32061.64</v>
+        <v>32011.95</v>
       </c>
     </row>
     <row r="720">
@@ -44375,7 +44375,7 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>2244.32</v>
+        <v>2240.84</v>
       </c>
     </row>
     <row r="721">
@@ -44436,7 +44436,7 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>3997.8</v>
+        <v>3991.6</v>
       </c>
     </row>
     <row r="722">
@@ -44497,7 +44497,7 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>2671.8</v>
+        <v>2667.66</v>
       </c>
     </row>
     <row r="723">
@@ -44558,7 +44558,7 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>2244.32</v>
+        <v>2240.84</v>
       </c>
     </row>
     <row r="724">
@@ -44619,7 +44619,7 @@
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>2244.32</v>
+        <v>2240.84</v>
       </c>
     </row>
     <row r="725">
@@ -44680,7 +44680,7 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>13893.38</v>
+        <v>13871.85</v>
       </c>
     </row>
     <row r="726">
@@ -44741,7 +44741,7 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>8549.77</v>
+        <v>8536.52</v>
       </c>
     </row>
     <row r="727">
@@ -44802,7 +44802,7 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>8549.77</v>
+        <v>8593.93</v>
       </c>
     </row>
     <row r="728">
@@ -44863,7 +44863,7 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>2671.8</v>
+        <v>2685.6</v>
       </c>
     </row>
     <row r="729">
@@ -44924,7 +44924,7 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>2244.32</v>
+        <v>2255.91</v>
       </c>
     </row>
     <row r="730">
@@ -44985,7 +44985,7 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>6519.2</v>
+        <v>6552.87</v>
       </c>
     </row>
     <row r="731">
@@ -45046,7 +45046,7 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>21374.43</v>
+        <v>21484.82</v>
       </c>
     </row>
     <row r="732">
@@ -45107,7 +45107,7 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>2707.71</v>
+        <v>2721.7</v>
       </c>
     </row>
     <row r="733">
@@ -45168,7 +45168,7 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>9510.98</v>
+        <v>9560.1</v>
       </c>
     </row>
     <row r="734">
@@ -45229,7 +45229,7 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>3206.16</v>
+        <v>3222.72</v>
       </c>
     </row>
     <row r="735">
@@ -45290,7 +45290,7 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>4274.89</v>
+        <v>4296.96</v>
       </c>
     </row>
     <row r="736">
@@ -45351,7 +45351,7 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>10687.21</v>
+        <v>10742.41</v>
       </c>
     </row>
     <row r="737">
@@ -45412,7 +45412,7 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>13893.38</v>
+        <v>13965.13</v>
       </c>
     </row>
     <row r="738">
@@ -45473,7 +45473,7 @@
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>2671.8</v>
+        <v>2685.6</v>
       </c>
     </row>
     <row r="739">
@@ -45534,7 +45534,7 @@
         </is>
       </c>
       <c r="M739" s="2" t="n">
-        <v>4274.89</v>
+        <v>4296.96</v>
       </c>
     </row>
     <row r="740">
@@ -45595,7 +45595,7 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>2244.32</v>
+        <v>2255.91</v>
       </c>
     </row>
     <row r="741">
@@ -45656,7 +45656,7 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>2351.19</v>
+        <v>2363.33</v>
       </c>
     </row>
     <row r="742">
@@ -45717,7 +45717,7 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>7056.38</v>
+        <v>7092.83</v>
       </c>
     </row>
     <row r="743">
@@ -45778,7 +45778,7 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>14855.23</v>
+        <v>14931.95</v>
       </c>
     </row>
     <row r="744">
@@ -45839,7 +45839,7 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>6412.33</v>
+        <v>6445.44</v>
       </c>
     </row>
     <row r="745">
@@ -45900,7 +45900,7 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>2244.32</v>
+        <v>2255.91</v>
       </c>
     </row>
     <row r="746">
@@ -45961,7 +45961,7 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>42748.86</v>
+        <v>42969.63</v>
       </c>
     </row>
     <row r="747">
@@ -46022,7 +46022,7 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>6412.33</v>
+        <v>6445.44</v>
       </c>
     </row>
     <row r="748">
@@ -46083,7 +46083,7 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>11755.94</v>
+        <v>11816.65</v>
       </c>
     </row>
     <row r="749">
@@ -46144,7 +46144,7 @@
         </is>
       </c>
       <c r="M749" s="2" t="n">
-        <v>2351.19</v>
+        <v>2363.33</v>
       </c>
     </row>
     <row r="750">
@@ -46205,7 +46205,7 @@
         </is>
       </c>
       <c r="M750" s="2" t="n">
-        <v>6091.71</v>
+        <v>6123.17</v>
       </c>
     </row>
     <row r="751">
@@ -46266,7 +46266,7 @@
         </is>
       </c>
       <c r="M751" s="2" t="n">
-        <v>21374.43</v>
+        <v>21484.81</v>
       </c>
     </row>
     <row r="752">
@@ -46327,7 +46327,7 @@
         </is>
       </c>
       <c r="M752" s="2" t="n">
-        <v>4274.89</v>
+        <v>4296.96</v>
       </c>
     </row>
     <row r="753">
@@ -46388,7 +46388,7 @@
         </is>
       </c>
       <c r="M753" s="2" t="n">
-        <v>7053.56</v>
+        <v>7089.99</v>
       </c>
     </row>
     <row r="754">
@@ -46449,7 +46449,7 @@
         </is>
       </c>
       <c r="M754" s="2" t="n">
-        <v>6091.71</v>
+        <v>6123.17</v>
       </c>
     </row>
     <row r="755">
@@ -46510,7 +46510,7 @@
         </is>
       </c>
       <c r="M755" s="2" t="n">
-        <v>4274.89</v>
+        <v>4296.96</v>
       </c>
     </row>
     <row r="756">
@@ -46571,7 +46571,7 @@
         </is>
       </c>
       <c r="M756" s="2" t="n">
-        <v>2229.63</v>
+        <v>2241.15</v>
       </c>
     </row>
     <row r="757">
@@ -46632,7 +46632,7 @@
         </is>
       </c>
       <c r="M757" s="2" t="n">
-        <v>2671.8</v>
+        <v>2685.6</v>
       </c>
     </row>
     <row r="758">
@@ -46693,7 +46693,7 @@
         </is>
       </c>
       <c r="M758" s="2" t="n">
-        <v>7481.05</v>
+        <v>7519.69</v>
       </c>
     </row>
     <row r="759">
@@ -46754,7 +46754,7 @@
         </is>
       </c>
       <c r="M759" s="2" t="n">
-        <v>6412.33</v>
+        <v>6445.44</v>
       </c>
     </row>
     <row r="760">
@@ -46815,7 +46815,7 @@
         </is>
       </c>
       <c r="M760" s="2" t="n">
-        <v>2244.32</v>
+        <v>2255.91</v>
       </c>
     </row>
     <row r="761">
@@ -46876,7 +46876,7 @@
         </is>
       </c>
       <c r="M761" s="2" t="n">
-        <v>2244.32</v>
+        <v>2255.91</v>
       </c>
     </row>
     <row r="762">
@@ -46937,7 +46937,7 @@
         </is>
       </c>
       <c r="M762" s="2" t="n">
-        <v>3206.16</v>
+        <v>3222.72</v>
       </c>
     </row>
     <row r="763">
@@ -46998,7 +46998,7 @@
         </is>
       </c>
       <c r="M763" s="2" t="n">
-        <v>42748.86</v>
+        <v>42969.63</v>
       </c>
     </row>
     <row r="764">
@@ -47059,7 +47059,7 @@
         </is>
       </c>
       <c r="M764" s="2" t="n">
-        <v>5343.61</v>
+        <v>5381.32</v>
       </c>
     </row>
     <row r="765">
@@ -47120,7 +47120,7 @@
         </is>
       </c>
       <c r="M765" s="2" t="n">
-        <v>5343.61</v>
+        <v>5381.32</v>
       </c>
     </row>
     <row r="766">
@@ -47181,7 +47181,7 @@
         </is>
       </c>
       <c r="M766" s="2" t="n">
-        <v>4274.89</v>
+        <v>4305.06</v>
       </c>
     </row>
     <row r="767">
@@ -47242,7 +47242,7 @@
         </is>
       </c>
       <c r="M767" s="2" t="n">
-        <v>2244.32</v>
+        <v>2260.15</v>
       </c>
     </row>
     <row r="768">
@@ -47303,7 +47303,7 @@
         </is>
       </c>
       <c r="M768" s="2" t="n">
-        <v>4274.89</v>
+        <v>4305.06</v>
       </c>
     </row>
     <row r="769">
@@ -47364,7 +47364,7 @@
         </is>
       </c>
       <c r="M769" s="2" t="n">
-        <v>2564.93</v>
+        <v>2583.03</v>
       </c>
     </row>
     <row r="770">
@@ -47425,7 +47425,7 @@
         </is>
       </c>
       <c r="M770" s="2" t="n">
-        <v>3100.65</v>
+        <v>3122.53</v>
       </c>
     </row>
     <row r="771">
@@ -47486,7 +47486,7 @@
         </is>
       </c>
       <c r="M771" s="2" t="n">
-        <v>24046.23</v>
+        <v>24215.94</v>
       </c>
     </row>
     <row r="772">
@@ -47547,7 +47547,7 @@
         </is>
       </c>
       <c r="M772" s="2" t="n">
-        <v>2308.44</v>
+        <v>2324.73</v>
       </c>
     </row>
     <row r="773">
@@ -47608,7 +47608,7 @@
         </is>
       </c>
       <c r="M773" s="2" t="n">
-        <v>5343.61</v>
+        <v>5381.32</v>
       </c>
     </row>
     <row r="774">
@@ -47669,7 +47669,7 @@
         </is>
       </c>
       <c r="M774" s="2" t="n">
-        <v>32061.64</v>
+        <v>32287.92</v>
       </c>
     </row>
     <row r="775">
@@ -47730,7 +47730,7 @@
         </is>
       </c>
       <c r="M775" s="2" t="n">
-        <v>3099.29</v>
+        <v>3121.17</v>
       </c>
     </row>
     <row r="776">
@@ -47791,7 +47791,7 @@
         </is>
       </c>
       <c r="M776" s="2" t="n">
-        <v>10687.21</v>
+        <v>10762.64</v>
       </c>
     </row>
     <row r="777">
@@ -47852,7 +47852,7 @@
         </is>
       </c>
       <c r="M777" s="2" t="n">
-        <v>7645.6</v>
+        <v>7699.56</v>
       </c>
     </row>
     <row r="778">
@@ -47913,7 +47913,7 @@
         </is>
       </c>
       <c r="M778" s="2" t="n">
-        <v>5343.61</v>
+        <v>5381.32</v>
       </c>
     </row>
     <row r="779">
@@ -47974,7 +47974,7 @@
         </is>
       </c>
       <c r="M779" s="2" t="n">
-        <v>3206.16</v>
+        <v>3228.79</v>
       </c>
     </row>
     <row r="780">
@@ -48035,7 +48035,7 @@
         </is>
       </c>
       <c r="M780" s="2" t="n">
-        <v>8705.17</v>
+        <v>8766.610000000001</v>
       </c>
     </row>
     <row r="781">
@@ -48096,7 +48096,7 @@
         </is>
       </c>
       <c r="M781" s="2" t="n">
-        <v>2671.8</v>
+        <v>2690.66</v>
       </c>
     </row>
     <row r="782">
@@ -48157,7 +48157,7 @@
         </is>
       </c>
       <c r="M782" s="2" t="n">
-        <v>2426.29</v>
+        <v>2443.41</v>
       </c>
     </row>
     <row r="783">
@@ -48218,7 +48218,7 @@
         </is>
       </c>
       <c r="M783" s="2" t="n">
-        <v>2671.8</v>
+        <v>2690.66</v>
       </c>
     </row>
     <row r="784">
@@ -48279,7 +48279,7 @@
         </is>
       </c>
       <c r="M784" s="2" t="n">
-        <v>5343.61</v>
+        <v>5381.32</v>
       </c>
     </row>
     <row r="785">
@@ -48340,7 +48340,7 @@
         </is>
       </c>
       <c r="M785" s="2" t="n">
-        <v>2244.32</v>
+        <v>2260.15</v>
       </c>
     </row>
     <row r="786">
@@ -48401,7 +48401,7 @@
         </is>
       </c>
       <c r="M786" s="2" t="n">
-        <v>8763.52</v>
+        <v>8825.370000000001</v>
       </c>
     </row>
     <row r="787">
@@ -48462,7 +48462,7 @@
         </is>
       </c>
       <c r="M787" s="2" t="n">
-        <v>7481.05</v>
+        <v>7533.85</v>
       </c>
     </row>
     <row r="788">
@@ -48523,7 +48523,7 @@
         </is>
       </c>
       <c r="M788" s="2" t="n">
-        <v>5343.61</v>
+        <v>5381.32</v>
       </c>
     </row>
     <row r="789">
@@ -48584,7 +48584,7 @@
         </is>
       </c>
       <c r="M789" s="2" t="n">
-        <v>3206.16</v>
+        <v>3228.79</v>
       </c>
     </row>
     <row r="790">
@@ -48645,7 +48645,7 @@
         </is>
       </c>
       <c r="M790" s="2" t="n">
-        <v>8549.77</v>
+        <v>8610.110000000001</v>
       </c>
     </row>
     <row r="791">
@@ -48706,7 +48706,7 @@
         </is>
       </c>
       <c r="M791" s="2" t="n">
-        <v>12824.66</v>
+        <v>12915.17</v>
       </c>
     </row>
     <row r="792">
@@ -48767,7 +48767,7 @@
         </is>
       </c>
       <c r="M792" s="2" t="n">
-        <v>4061.14</v>
+        <v>4089.8</v>
       </c>
     </row>
     <row r="793">
@@ -48828,7 +48828,7 @@
         </is>
       </c>
       <c r="M793" s="2" t="n">
-        <v>7481.05</v>
+        <v>7533.85</v>
       </c>
     </row>
     <row r="794">
@@ -48889,7 +48889,7 @@
         </is>
       </c>
       <c r="M794" s="2" t="n">
-        <v>21374.43</v>
+        <v>21525.28</v>
       </c>
     </row>
     <row r="795">
@@ -48950,7 +48950,7 @@
         </is>
       </c>
       <c r="M795" s="2" t="n">
-        <v>3206.16</v>
+        <v>3228.79</v>
       </c>
     </row>
     <row r="796">
@@ -49011,7 +49011,7 @@
         </is>
       </c>
       <c r="M796" s="2" t="n">
-        <v>3206.16</v>
+        <v>3228.79</v>
       </c>
     </row>
     <row r="797">
@@ -49072,7 +49072,7 @@
         </is>
       </c>
       <c r="M797" s="2" t="n">
-        <v>2671.8</v>
+        <v>2690.66</v>
       </c>
     </row>
     <row r="798">
@@ -49133,7 +49133,7 @@
         </is>
       </c>
       <c r="M798" s="2" t="n">
-        <v>44886.3</v>
+        <v>45203.09</v>
       </c>
     </row>
     <row r="799">
@@ -49194,7 +49194,7 @@
         </is>
       </c>
       <c r="M799" s="2" t="n">
-        <v>2244.32</v>
+        <v>2260.15</v>
       </c>
     </row>
     <row r="800">
@@ -49255,7 +49255,7 @@
         </is>
       </c>
       <c r="M800" s="2" t="n">
-        <v>3206.16</v>
+        <v>3228.79</v>
       </c>
     </row>
     <row r="801">
@@ -49316,7 +49316,7 @@
         </is>
       </c>
       <c r="M801" s="2" t="n">
-        <v>8549.77</v>
+        <v>8610.110000000001</v>
       </c>
     </row>
     <row r="802">
@@ -49377,7 +49377,7 @@
         </is>
       </c>
       <c r="M802" s="2" t="n">
-        <v>6412.33</v>
+        <v>6457.58</v>
       </c>
     </row>
     <row r="803">
@@ -49438,7 +49438,7 @@
         </is>
       </c>
       <c r="M803" s="2" t="n">
-        <v>2800.05</v>
+        <v>2819.81</v>
       </c>
     </row>
     <row r="804">
@@ -49499,7 +49499,7 @@
         </is>
       </c>
       <c r="M804" s="2" t="n">
-        <v>3369.68</v>
+        <v>3393.46</v>
       </c>
     </row>
     <row r="805">
@@ -49560,7 +49560,7 @@
         </is>
       </c>
       <c r="M805" s="2" t="n">
-        <v>4702.37</v>
+        <v>4735.56</v>
       </c>
     </row>
     <row r="806">
@@ -49621,7 +49621,7 @@
         </is>
       </c>
       <c r="M806" s="2" t="n">
-        <v>4274.89</v>
+        <v>4305.06</v>
       </c>
     </row>
     <row r="807">
@@ -49682,7 +49682,7 @@
         </is>
       </c>
       <c r="M807" s="2" t="n">
-        <v>21374.43</v>
+        <v>21525.28</v>
       </c>
     </row>
     <row r="808">
@@ -49743,7 +49743,7 @@
         </is>
       </c>
       <c r="M808" s="2" t="n">
-        <v>2671.8</v>
+        <v>2690.66</v>
       </c>
     </row>
     <row r="809">
@@ -49804,7 +49804,7 @@
         </is>
       </c>
       <c r="M809" s="2" t="n">
-        <v>15496.46</v>
+        <v>15605.83</v>
       </c>
     </row>
     <row r="810">
@@ -49865,7 +49865,7 @@
         </is>
       </c>
       <c r="M810" s="2" t="n">
-        <v>4141.3</v>
+        <v>4170.52</v>
       </c>
     </row>
     <row r="811">
@@ -49926,7 +49926,7 @@
         </is>
       </c>
       <c r="M811" s="2" t="n">
-        <v>10420.03</v>
+        <v>10493.57</v>
       </c>
     </row>
     <row r="812">
@@ -49987,7 +49987,7 @@
         </is>
       </c>
       <c r="M812" s="2" t="n">
-        <v>2229.63</v>
+        <v>2245.37</v>
       </c>
     </row>
     <row r="813">
@@ -50048,7 +50048,7 @@
         </is>
       </c>
       <c r="M813" s="2" t="n">
-        <v>22507.27</v>
+        <v>22666.12</v>
       </c>
     </row>
     <row r="814">
@@ -50109,7 +50109,7 @@
         </is>
       </c>
       <c r="M814" s="2" t="n">
-        <v>12824.66</v>
+        <v>12915.17</v>
       </c>
     </row>
     <row r="815">
@@ -50170,7 +50170,7 @@
         </is>
       </c>
       <c r="M815" s="2" t="n">
-        <v>9642.1</v>
+        <v>9710.15</v>
       </c>
     </row>
     <row r="816">
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="M816" s="2" t="n">
-        <v>7481.05</v>
+        <v>7533.85</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/suministro-de-combustibles/nov-2025.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/nov-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC nov-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC nov-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -11293,7 +11293,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -12147,7 +12147,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12635,7 +12635,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12757,7 +12757,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12818,7 +12818,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12879,7 +12879,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -13062,7 +13062,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13367,7 +13367,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -14038,7 +14038,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14404,7 +14404,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14709,7 +14709,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14892,7 +14892,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14953,7 +14953,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15563,7 +15563,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -16234,7 +16234,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16417,7 +16417,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -17027,7 +17027,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17149,7 +17149,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17210,7 +17210,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17515,7 +17515,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18735,7 +18735,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18979,7 +18979,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19345,7 +19345,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -20199,7 +20199,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20870,7 +20870,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -20992,7 +20992,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21480,7 +21480,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21968,7 +21968,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -22090,7 +22090,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22639,7 +22639,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -22944,7 +22944,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -23981,7 +23981,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -24042,7 +24042,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -24347,7 +24347,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -25384,7 +25384,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -25506,7 +25506,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25628,7 +25628,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -25872,7 +25872,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -25933,7 +25933,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -26726,7 +26726,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -28373,7 +28373,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -28800,7 +28800,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -29410,7 +29410,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -29532,7 +29532,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -29776,7 +29776,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -29898,7 +29898,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -30203,7 +30203,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -30630,7 +30630,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -31057,7 +31057,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -31301,7 +31301,7 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -31728,7 +31728,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -32155,7 +32155,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -33070,7 +33070,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -33924,7 +33924,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -33985,7 +33985,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -34534,7 +34534,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -34656,7 +34656,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -34900,7 +34900,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -35571,7 +35571,7 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -36608,7 +36608,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -37035,7 +37035,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -37157,7 +37157,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -37279,7 +37279,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -37584,7 +37584,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -37706,7 +37706,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -37767,7 +37767,7 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -37828,7 +37828,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -38072,7 +38072,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -38499,7 +38499,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -38621,7 +38621,7 @@
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
@@ -39048,7 +39048,7 @@
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -39109,7 +39109,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -39170,7 +39170,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -39475,7 +39475,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -39597,7 +39597,7 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -39841,7 +39841,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -40573,7 +40573,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -40695,7 +40695,7 @@
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I660" t="inlineStr">
@@ -40756,7 +40756,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -41183,7 +41183,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -41366,7 +41366,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -41549,7 +41549,7 @@
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -42342,7 +42342,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -42708,7 +42708,7 @@
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -42830,7 +42830,7 @@
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
@@ -43074,7 +43074,7 @@
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -43135,7 +43135,7 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -43196,7 +43196,7 @@
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -43318,7 +43318,7 @@
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -43623,7 +43623,7 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
@@ -43806,7 +43806,7 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
@@ -43989,7 +43989,7 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
@@ -44294,7 +44294,7 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
@@ -44416,7 +44416,7 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
@@ -45026,7 +45026,7 @@
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I731" t="inlineStr">
@@ -45209,7 +45209,7 @@
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
@@ -45331,7 +45331,7 @@
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
@@ -45453,7 +45453,7 @@
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
@@ -45514,7 +45514,7 @@
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
@@ -46185,7 +46185,7 @@
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
@@ -46307,7 +46307,7 @@
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
@@ -46490,7 +46490,7 @@
       </c>
       <c r="H755" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I755" t="inlineStr">
@@ -46673,7 +46673,7 @@
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I758" t="inlineStr">
@@ -47161,7 +47161,7 @@
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I766" t="inlineStr">
@@ -47832,7 +47832,7 @@
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I777" t="inlineStr">
@@ -48076,7 +48076,7 @@
       </c>
       <c r="H781" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I781" t="inlineStr">
@@ -48259,7 +48259,7 @@
       </c>
       <c r="H784" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I784" t="inlineStr">
@@ -48442,7 +48442,7 @@
       </c>
       <c r="H787" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I787" t="inlineStr">
@@ -48503,7 +48503,7 @@
       </c>
       <c r="H788" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I788" t="inlineStr">
@@ -48991,7 +48991,7 @@
       </c>
       <c r="H796" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I796" t="inlineStr">
@@ -49479,7 +49479,7 @@
       </c>
       <c r="H804" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I804" t="inlineStr">
@@ -49540,7 +49540,7 @@
       </c>
       <c r="H805" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I805" t="inlineStr">
@@ -49967,7 +49967,7 @@
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I812" t="inlineStr">

--- a/docs/oc-mensuales/suministro-de-combustibles/nov-2025.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/nov-2025.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Proyecto La Cisterna</t>
+          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNITARIA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TREHUACO DEPARTAMENTO</t>
+          <t>I MUNICIPALIDAD DE TREHUACO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION COMUNAL DE SALUD- CORP MARIA PINTO </t>
+          <t>CORPORACION MUNICIPAL DE MARÍA PINTO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION COMUNAL DE EDUCACION - CORP MARIA PINTO </t>
+          <t>CORPORACION MUNICIPAL DE MARÍA PINTO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE SAN NICOLAS - DEPTO. DE SALUD</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE QUILLÓN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Región Metropolitana" - B Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SEREMI Bienes Nacionales III Región</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>I.Municipalidad de San Pablo -Salud</t>
+          <t>I MUNICIPALIDAD DE SAN PABLO</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>HOSPITAL COMUNITARIO CRISTINA CALDERON DE PUERTO WILLIAMS</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LUMACO</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>I MUNICIPALIDAD DE TUCAPEL</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE PUNTA ARENAS</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hospital de Peñaflor</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10190,7 +10190,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Trehuaco - Salud</t>
+          <t>I MUNICIPALIDAD DE TREHUACO</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Valparaíso" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GALVARINO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11471,7 +11471,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Tesorería Regional Rancagua</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11776,7 +11776,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Departamento de Educación</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12447,7 +12447,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LITUECHE</t>
+          <t>Hospital de Litueche</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12752,7 +12752,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Menores</t>
+          <t>SERVICIO NACIONAL DE MENORES</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13179,7 +13179,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13240,7 +13240,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13423,7 +13423,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Tesorería Provincial de Valdivia</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13850,7 +13850,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Departamento de Educación</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14033,7 +14033,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE PLANIFICACION Y COORD. VIII REGION</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -14643,7 +14643,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONTULMO</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONTULMO</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Río Negro - Salud</t>
+          <t>I MUNICIPALIDAD DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15436,7 +15436,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Tesorería Regional de V Región</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -17144,7 +17144,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Tesorería Regional de Magalllanes y Antártica Chil</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17266,12 +17266,12 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17815,7 +17815,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18242,7 +18242,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Municipalidad de Yerbas Buenas-Depto. Educación</t>
+          <t>Ilustre Municipalidad de Yerbas Buenas</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -18364,7 +18364,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -18852,7 +18852,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NIQUEN</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -18974,7 +18974,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONTULMO</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -19279,7 +19279,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Regional Min.Bs.Nac. XIV Región Los Rios</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -19340,7 +19340,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Tesorería Regional Concepción</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -19828,7 +19828,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Tesorería Regional de Talca</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -20011,7 +20011,7 @@
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Tesorería Regional de Talca</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -20560,7 +20560,7 @@
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -21109,7 +21109,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>SERPLAC X REGION</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -21353,7 +21353,7 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>SERPLAC XI Región</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -21414,7 +21414,7 @@
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Municipalidad de Yerbas Buenas-Depto. Salud</t>
+          <t>Ilustre Municipalidad de Yerbas Buenas</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -21597,7 +21597,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -22207,7 +22207,7 @@
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Tesorería Regional de Coquimbo - La Serena</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -22268,7 +22268,7 @@
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Tesorería Regional de Aysén</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -22329,7 +22329,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Tesorería Regional de Coquimbo - La Serena</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -22573,7 +22573,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -22695,7 +22695,7 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>SECRETARIA REG MINIST DE BIENES NACIONAL I REGION</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -23000,7 +23000,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -23488,7 +23488,7 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
@@ -23732,7 +23732,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -23915,7 +23915,7 @@
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -24037,7 +24037,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>CORPORACIÓN SOCIAL Y CULTURAL DE CONCEPCIÓN-SEMCO</t>
+          <t>CORPORACION SOCIAL Y CULTURA DE CONCEPCION - SEMCO</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>Hospital Comunitario de Salud Familiar de Bulnes</t>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -25135,7 +25135,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>MOP Dirección General de Concesiones</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -25257,7 +25257,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -25440,7 +25440,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cochamó - Salud</t>
+          <t>ILUSTRE MUNICIPALIDAD COCHAMO</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -25562,7 +25562,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -25623,7 +25623,7 @@
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -26055,7 +26055,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -26599,7 +26599,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>TESORERIA REGIONAL ANTOFAGASTA</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -26782,7 +26782,7 @@
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>SERPLAC II REGION</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -27026,7 +27026,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>Tesroreria Regional de La Araucania</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -27209,7 +27209,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>Tesroreria Regional de La Araucania</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -27331,7 +27331,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -27697,7 +27697,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -28002,12 +28002,12 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -28307,7 +28307,7 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>Corporación del Deporte e Inclusión Social de la I</t>
+          <t>Corporación del Deporte e Inclusión Social de la Ilustre Municipalidad de Cerro Navia</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
@@ -28612,7 +28612,7 @@
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
@@ -28673,7 +28673,7 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Putre</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
@@ -28978,7 +28978,7 @@
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
@@ -29100,7 +29100,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>Tesoreria Regional X Región - Pto Montt</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -29222,7 +29222,7 @@
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -29588,7 +29588,7 @@
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE REDES ASISTENCIALES</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
@@ -30442,7 +30442,7 @@
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
@@ -30686,7 +30686,7 @@
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>Gestión del Riesgo de Desastres</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
@@ -30869,7 +30869,7 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
@@ -30991,7 +30991,7 @@
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>Departamento Administrativo de Salud Municipal.</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
@@ -31235,7 +31235,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
@@ -31296,7 +31296,7 @@
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>Departamento Comunal de Salud</t>
+          <t>I MUNICIPALIDAD DE TUCAPEL</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
@@ -31418,7 +31418,7 @@
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
@@ -32028,7 +32028,7 @@
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H518" t="inlineStr">
@@ -33004,7 +33004,7 @@
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
@@ -33187,7 +33187,7 @@
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H537" t="inlineStr">
@@ -33436,7 +33436,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -33492,7 +33492,7 @@
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>Tesorería Provincial de Ñuble - Chillán</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
@@ -34041,7 +34041,7 @@
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Penco - Salud</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
@@ -34163,7 +34163,7 @@
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H553" t="inlineStr">
@@ -34773,7 +34773,7 @@
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>Tesorería Regional de Atacama-Copiapó</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
@@ -35139,7 +35139,7 @@
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H569" t="inlineStr">
@@ -35444,7 +35444,7 @@
       </c>
       <c r="G574" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H574" t="inlineStr">
@@ -35505,7 +35505,7 @@
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H575" t="inlineStr">
@@ -35749,7 +35749,7 @@
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Río Negro - Educación</t>
+          <t>I MUNICIPALIDAD DE RIO NEGRO</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
@@ -36542,7 +36542,7 @@
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H592" t="inlineStr">
@@ -37091,7 +37091,7 @@
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GORBEA</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
@@ -37325,7 +37325,7 @@
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F605" t="inlineStr">
@@ -37518,7 +37518,7 @@
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región de los Lagos</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H608" t="inlineStr">
@@ -37823,7 +37823,7 @@
       </c>
       <c r="G613" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE EDUCACION XII REGION</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H613" t="inlineStr">
@@ -38067,7 +38067,7 @@
       </c>
       <c r="G617" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Pta. Arenas</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H617" t="inlineStr">
@@ -38433,7 +38433,7 @@
       </c>
       <c r="G623" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H623" t="inlineStr">
@@ -38555,7 +38555,7 @@
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
         </is>
       </c>
       <c r="H625" t="inlineStr">
@@ -38743,7 +38743,7 @@
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -39104,7 +39104,7 @@
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H634" t="inlineStr">
@@ -39165,7 +39165,7 @@
       </c>
       <c r="G635" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H635" t="inlineStr">
@@ -39226,7 +39226,7 @@
       </c>
       <c r="G636" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H636" t="inlineStr">
@@ -39348,7 +39348,7 @@
       </c>
       <c r="G638" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región de Aysen</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H638" t="inlineStr">
@@ -39536,7 +39536,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -39775,7 +39775,7 @@
       </c>
       <c r="G645" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE BIENES NACIONALES II REGION</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H645" t="inlineStr">
@@ -39897,7 +39897,7 @@
       </c>
       <c r="G647" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H647" t="inlineStr">
@@ -39958,7 +39958,7 @@
       </c>
       <c r="G648" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Región Metropolitana</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H648" t="inlineStr">
@@ -40324,7 +40324,7 @@
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
@@ -40568,7 +40568,7 @@
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
@@ -40751,7 +40751,7 @@
       </c>
       <c r="G661" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H661" t="inlineStr">
@@ -41483,7 +41483,7 @@
       </c>
       <c r="G673" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Putre</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
         </is>
       </c>
       <c r="H673" t="inlineStr">
@@ -41788,7 +41788,7 @@
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H678" t="inlineStr">
@@ -41854,7 +41854,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -41915,7 +41915,7 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -41971,7 +41971,7 @@
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE PUERTO MONTT</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H681" t="inlineStr">
@@ -42093,7 +42093,7 @@
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
@@ -42398,7 +42398,7 @@
       </c>
       <c r="G688" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H688" t="inlineStr">
@@ -42886,7 +42886,7 @@
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H696" t="inlineStr">
@@ -43252,7 +43252,7 @@
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H702" t="inlineStr">
@@ -43313,7 +43313,7 @@
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL BIENES NACIONALES VI REGION</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
@@ -43557,7 +43557,7 @@
       </c>
       <c r="G707" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H707" t="inlineStr">
@@ -44228,7 +44228,7 @@
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H718" t="inlineStr">
@@ -44350,7 +44350,7 @@
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo de Vilcún</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H720" t="inlineStr">
@@ -44472,7 +44472,7 @@
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GORBEA</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H722" t="inlineStr">
@@ -44838,7 +44838,7 @@
       </c>
       <c r="G728" t="inlineStr">
         <is>
-          <t>Tesorería Regional de Tarapacá</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H728" t="inlineStr">
@@ -45021,7 +45021,7 @@
       </c>
       <c r="G731" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Curanilahue - Salud</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H731" t="inlineStr">
@@ -45204,7 +45204,7 @@
       </c>
       <c r="G734" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Contulmo - Educación</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H734" t="inlineStr">
@@ -45753,7 +45753,7 @@
       </c>
       <c r="G743" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H743" t="inlineStr">
@@ -45875,7 +45875,7 @@
       </c>
       <c r="G745" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H745" t="inlineStr">
@@ -46302,7 +46302,7 @@
       </c>
       <c r="G752" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Santa Barbara - Salud</t>
+          <t>I MUNICIPALIDAD DE SANTA BARBARA</t>
         </is>
       </c>
       <c r="H752" t="inlineStr">
@@ -46729,7 +46729,7 @@
       </c>
       <c r="G759" t="inlineStr">
         <is>
-          <t>Dirección Regional de Ñuble</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H759" t="inlineStr">
@@ -46912,7 +46912,7 @@
       </c>
       <c r="G762" t="inlineStr">
         <is>
-          <t>COMISION CHILENA DE ENERGIA NUCLEAR</t>
+          <t>Comisión Chilena de Energía Nuclear</t>
         </is>
       </c>
       <c r="H762" t="inlineStr">
@@ -47705,7 +47705,7 @@
       </c>
       <c r="G775" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H775" t="inlineStr">
@@ -47827,7 +47827,7 @@
       </c>
       <c r="G777" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE TALCAHUANO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H777" t="inlineStr">
@@ -48071,7 +48071,7 @@
       </c>
       <c r="G781" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO DEPARTAMENTO DE SALUD</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H781" t="inlineStr">
@@ -48498,7 +48498,7 @@
       </c>
       <c r="G788" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE MULCHEN DIRECCION DE SALUD MUNICIPAL</t>
+          <t>I MUNICIPALIDAD DE MULCHEN</t>
         </is>
       </c>
       <c r="H788" t="inlineStr">
@@ -48742,7 +48742,7 @@
       </c>
       <c r="G792" t="inlineStr">
         <is>
-          <t>ADMINISTRACIÓN ADUANA DE ARICA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H792" t="inlineStr">
@@ -48986,7 +48986,7 @@
       </c>
       <c r="G796" t="inlineStr">
         <is>
-          <t>SERPLAC VI Región</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H796" t="inlineStr">
@@ -49047,7 +49047,7 @@
       </c>
       <c r="G797" t="inlineStr">
         <is>
-          <t>Agencia de Promocion de la inversion extranjera</t>
+          <t>AGENCIA DE PROMOCION DE LA INVERSION EXTRANJERA</t>
         </is>
       </c>
       <c r="H797" t="inlineStr">
@@ -49352,7 +49352,7 @@
       </c>
       <c r="G802" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE VALPARAISO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H802" t="inlineStr">
@@ -49586,7 +49586,7 @@
       </c>
       <c r="E806" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F806" t="inlineStr">
@@ -49718,7 +49718,7 @@
       </c>
       <c r="G808" t="inlineStr">
         <is>
-          <t>Direc.Reg.Arica y Parinacota</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H808" t="inlineStr">
